--- a/data/Specimens_info.xlsx
+++ b/data/Specimens_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katja.oselj\Documents\GitHub\P.murcianus_geometric_morphometrics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7FE3BF-9377-4C9A-9193-7B4C2EB07817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A65525-9082-4428-B44C-BA96D31E657E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{40579A1C-AC2A-4664-B5AB-7D3138A89E38}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{40579A1C-AC2A-4664-B5AB-7D3138A89E38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2711,8 +2711,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3069,7 +3070,7 @@
       <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
@@ -3090,7 +3091,7 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>869</v>
@@ -3110,7 +3111,7 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>869</v>
@@ -3130,7 +3131,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>869</v>
@@ -3150,7 +3151,7 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
         <v>869</v>
@@ -3170,7 +3171,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>869</v>
@@ -3190,7 +3191,7 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
         <v>869</v>
@@ -3210,7 +3211,7 @@
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
         <v>869</v>
@@ -3230,7 +3231,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
         <v>869</v>
@@ -3250,7 +3251,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>869</v>
@@ -3270,7 +3271,7 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>869</v>
@@ -3290,7 +3291,7 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
         <v>869</v>
@@ -3310,7 +3311,7 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>869</v>
@@ -3330,7 +3331,7 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
         <v>869</v>
@@ -3350,7 +3351,7 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
         <v>869</v>
@@ -3370,7 +3371,7 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
         <v>869</v>
@@ -3390,7 +3391,7 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
         <v>869</v>
@@ -3410,7 +3411,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
         <v>869</v>
@@ -3430,7 +3431,7 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
         <v>869</v>
@@ -3450,7 +3451,7 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>869</v>
@@ -3470,7 +3471,7 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>869</v>
@@ -3490,7 +3491,7 @@
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
         <v>869</v>
@@ -3510,7 +3511,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
         <v>869</v>
@@ -3530,7 +3531,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
         <v>869</v>
@@ -3550,7 +3551,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
         <v>869</v>
@@ -3570,7 +3571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
         <v>869</v>
@@ -3590,7 +3591,7 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
         <v>869</v>
@@ -3610,7 +3611,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
         <v>869</v>
@@ -3630,7 +3631,7 @@
         <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>869</v>
@@ -3650,7 +3651,7 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
         <v>869</v>
@@ -3670,7 +3671,7 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
         <v>869</v>
@@ -3690,7 +3691,7 @@
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
         <v>869</v>
@@ -3710,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
         <v>869</v>
@@ -3730,7 +3731,7 @@
         <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>869</v>
@@ -3750,7 +3751,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>869</v>
@@ -3770,7 +3771,7 @@
         <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
         <v>869</v>
@@ -3790,7 +3791,7 @@
         <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
         <v>869</v>
@@ -3810,7 +3811,7 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
         <v>869</v>
@@ -3830,7 +3831,7 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>869</v>
@@ -3850,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>869</v>
@@ -3870,7 +3871,7 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
         <v>869</v>
@@ -3890,7 +3891,7 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
         <v>869</v>
@@ -3910,7 +3911,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
         <v>869</v>
@@ -3930,7 +3931,7 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F44" t="s">
         <v>869</v>
@@ -3950,7 +3951,7 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F45" t="s">
         <v>869</v>
@@ -3970,7 +3971,7 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F46" t="s">
         <v>869</v>
@@ -3990,7 +3991,7 @@
         <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
         <v>869</v>
@@ -4010,7 +4011,7 @@
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
         <v>869</v>
@@ -4030,7 +4031,7 @@
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
         <v>869</v>
@@ -4050,7 +4051,7 @@
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F50" t="s">
         <v>869</v>
@@ -4070,7 +4071,7 @@
         <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51" t="s">
         <v>869</v>
@@ -4090,7 +4091,7 @@
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F52" t="s">
         <v>869</v>
@@ -4110,7 +4111,7 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
         <v>869</v>
@@ -4130,7 +4131,7 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
         <v>869</v>
@@ -4150,7 +4151,7 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F55" t="s">
         <v>869</v>
@@ -4170,7 +4171,7 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
         <v>869</v>
@@ -4190,7 +4191,7 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F57" t="s">
         <v>869</v>
@@ -4210,7 +4211,7 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>869</v>
@@ -4230,7 +4231,7 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F59" t="s">
         <v>869</v>
@@ -4250,7 +4251,7 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F60" t="s">
         <v>869</v>
@@ -4270,7 +4271,7 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
         <v>869</v>
@@ -4290,7 +4291,7 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F62" t="s">
         <v>869</v>
@@ -4310,7 +4311,7 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F63" t="s">
         <v>869</v>
@@ -4330,7 +4331,7 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
         <v>869</v>
@@ -4350,7 +4351,7 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F65" t="s">
         <v>869</v>
@@ -4370,7 +4371,7 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F66" t="s">
         <v>869</v>
@@ -4390,7 +4391,7 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F67" t="s">
         <v>869</v>
@@ -4410,7 +4411,7 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
         <v>869</v>
@@ -4430,7 +4431,7 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F69" t="s">
         <v>869</v>
@@ -4450,7 +4451,7 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
         <v>869</v>
@@ -4470,7 +4471,7 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F71" t="s">
         <v>869</v>
@@ -4490,7 +4491,7 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F72" t="s">
         <v>869</v>
@@ -4510,7 +4511,7 @@
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="s">
         <v>869</v>
@@ -4530,7 +4531,7 @@
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
         <v>869</v>
@@ -4550,7 +4551,7 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F75" t="s">
         <v>869</v>
@@ -4570,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>869</v>
@@ -4590,7 +4591,7 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
         <v>869</v>
@@ -4610,7 +4611,7 @@
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F78" t="s">
         <v>869</v>
@@ -4630,7 +4631,7 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F79" t="s">
         <v>869</v>
@@ -4650,7 +4651,7 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F80" t="s">
         <v>869</v>
@@ -4670,7 +4671,7 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F81" t="s">
         <v>869</v>
@@ -4690,7 +4691,7 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F82" t="s">
         <v>869</v>
@@ -4710,7 +4711,7 @@
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F83" t="s">
         <v>869</v>
@@ -4730,7 +4731,7 @@
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F84" t="s">
         <v>869</v>
@@ -4750,7 +4751,7 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
         <v>869</v>
@@ -4770,7 +4771,7 @@
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F86" t="s">
         <v>869</v>
@@ -4790,7 +4791,7 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
         <v>869</v>
@@ -4810,7 +4811,7 @@
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F88" t="s">
         <v>869</v>
@@ -4830,7 +4831,7 @@
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F89" t="s">
         <v>869</v>
@@ -4850,7 +4851,7 @@
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
         <v>869</v>
@@ -4870,7 +4871,7 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
         <v>869</v>
@@ -4890,7 +4891,7 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F92" t="s">
         <v>869</v>
@@ -4910,7 +4911,7 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F93" t="s">
         <v>869</v>
@@ -4930,7 +4931,7 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F94" t="s">
         <v>869</v>
@@ -4950,7 +4951,7 @@
         <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F95" t="s">
         <v>869</v>
@@ -4970,7 +4971,7 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F96" t="s">
         <v>869</v>
@@ -4990,7 +4991,7 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F97" t="s">
         <v>869</v>
@@ -5010,7 +5011,7 @@
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
         <v>869</v>
@@ -5030,7 +5031,7 @@
         <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
         <v>869</v>
@@ -5050,7 +5051,7 @@
         <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
         <v>869</v>
@@ -5070,7 +5071,7 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
         <v>869</v>
@@ -5090,7 +5091,7 @@
         <v>24</v>
       </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F102" t="s">
         <v>869</v>
@@ -5110,7 +5111,7 @@
         <v>24</v>
       </c>
       <c r="E103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F103" t="s">
         <v>869</v>
@@ -5130,7 +5131,7 @@
         <v>24</v>
       </c>
       <c r="E104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F104" t="s">
         <v>869</v>
@@ -5150,7 +5151,7 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F105" t="s">
         <v>869</v>
@@ -5170,7 +5171,7 @@
         <v>24</v>
       </c>
       <c r="E106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F106" t="s">
         <v>869</v>
@@ -5190,7 +5191,7 @@
         <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F107" t="s">
         <v>869</v>
@@ -5210,7 +5211,7 @@
         <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
         <v>869</v>
@@ -5230,7 +5231,7 @@
         <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F109" t="s">
         <v>869</v>
@@ -5250,7 +5251,7 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F110" t="s">
         <v>869</v>
@@ -5270,7 +5271,7 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
         <v>869</v>
@@ -5290,7 +5291,7 @@
         <v>24</v>
       </c>
       <c r="E112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F112" t="s">
         <v>869</v>
@@ -5310,7 +5311,7 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F113" t="s">
         <v>869</v>
@@ -5330,7 +5331,7 @@
         <v>24</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F114" t="s">
         <v>869</v>
@@ -5350,7 +5351,7 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F115" t="s">
         <v>869</v>
@@ -5370,7 +5371,7 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
         <v>869</v>
@@ -5390,7 +5391,7 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
         <v>869</v>
@@ -5410,7 +5411,7 @@
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
         <v>869</v>
@@ -5430,7 +5431,7 @@
         <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F119" t="s">
         <v>869</v>
@@ -5450,7 +5451,7 @@
         <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
         <v>869</v>
@@ -5470,7 +5471,7 @@
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F121" t="s">
         <v>869</v>
@@ -5490,7 +5491,7 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
         <v>869</v>
@@ -5510,7 +5511,7 @@
         <v>24</v>
       </c>
       <c r="E123" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
         <v>869</v>
@@ -5530,7 +5531,7 @@
         <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>869</v>
@@ -5550,7 +5551,7 @@
         <v>24</v>
       </c>
       <c r="E125" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s">
         <v>869</v>
@@ -5570,7 +5571,7 @@
         <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F126" t="s">
         <v>869</v>
@@ -5590,7 +5591,7 @@
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F127" t="s">
         <v>869</v>
@@ -5610,7 +5611,7 @@
         <v>24</v>
       </c>
       <c r="E128" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F128" t="s">
         <v>869</v>
@@ -5630,7 +5631,7 @@
         <v>24</v>
       </c>
       <c r="E129" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F129" t="s">
         <v>869</v>
@@ -5650,7 +5651,7 @@
         <v>24</v>
       </c>
       <c r="E130" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F130" t="s">
         <v>869</v>
@@ -5670,7 +5671,7 @@
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
         <v>869</v>
@@ -5690,7 +5691,7 @@
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F132" t="s">
         <v>869</v>
@@ -5710,7 +5711,7 @@
         <v>24</v>
       </c>
       <c r="E133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F133" t="s">
         <v>869</v>
@@ -5730,7 +5731,7 @@
         <v>24</v>
       </c>
       <c r="E134" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F134" t="s">
         <v>869</v>
@@ -5750,7 +5751,7 @@
         <v>24</v>
       </c>
       <c r="E135" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F135" t="s">
         <v>869</v>
@@ -5770,7 +5771,7 @@
         <v>24</v>
       </c>
       <c r="E136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F136" t="s">
         <v>869</v>
@@ -5790,7 +5791,7 @@
         <v>24</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F137" t="s">
         <v>869</v>
@@ -5810,7 +5811,7 @@
         <v>24</v>
       </c>
       <c r="E138" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F138" t="s">
         <v>869</v>
@@ -5830,7 +5831,7 @@
         <v>24</v>
       </c>
       <c r="E139" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F139" t="s">
         <v>869</v>
@@ -5850,7 +5851,7 @@
         <v>24</v>
       </c>
       <c r="E140" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F140" t="s">
         <v>869</v>
@@ -5870,7 +5871,7 @@
         <v>24</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F141" t="s">
         <v>869</v>
@@ -5890,7 +5891,7 @@
         <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F142" t="s">
         <v>869</v>
@@ -5910,7 +5911,7 @@
         <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F143" t="s">
         <v>869</v>
@@ -5930,7 +5931,7 @@
         <v>24</v>
       </c>
       <c r="E144" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F144" t="s">
         <v>869</v>
@@ -5950,7 +5951,7 @@
         <v>24</v>
       </c>
       <c r="E145" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F145" t="s">
         <v>869</v>
@@ -5970,7 +5971,7 @@
         <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F146" t="s">
         <v>869</v>
@@ -5990,7 +5991,7 @@
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F147" t="s">
         <v>869</v>
@@ -6010,7 +6011,7 @@
         <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s">
         <v>869</v>
@@ -6030,7 +6031,7 @@
         <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F149" t="s">
         <v>869</v>
@@ -6050,7 +6051,7 @@
         <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
         <v>869</v>
@@ -6070,7 +6071,7 @@
         <v>24</v>
       </c>
       <c r="E151" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F151" t="s">
         <v>869</v>
@@ -6090,7 +6091,7 @@
         <v>24</v>
       </c>
       <c r="E152" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F152" t="s">
         <v>869</v>
@@ -6110,7 +6111,7 @@
         <v>24</v>
       </c>
       <c r="E153" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F153" t="s">
         <v>869</v>
@@ -6130,7 +6131,7 @@
         <v>24</v>
       </c>
       <c r="E154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F154" t="s">
         <v>869</v>
@@ -6150,7 +6151,7 @@
         <v>24</v>
       </c>
       <c r="E155" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
         <v>869</v>
@@ -6170,7 +6171,7 @@
         <v>24</v>
       </c>
       <c r="E156" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F156" t="s">
         <v>869</v>
@@ -6190,7 +6191,7 @@
         <v>24</v>
       </c>
       <c r="E157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F157" t="s">
         <v>869</v>
@@ -6210,7 +6211,7 @@
         <v>24</v>
       </c>
       <c r="E158" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F158" t="s">
         <v>869</v>
@@ -6230,7 +6231,7 @@
         <v>24</v>
       </c>
       <c r="E159" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
         <v>869</v>
@@ -6250,7 +6251,7 @@
         <v>24</v>
       </c>
       <c r="E160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F160" t="s">
         <v>869</v>
@@ -6270,7 +6271,7 @@
         <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F161" t="s">
         <v>869</v>
@@ -6290,7 +6291,7 @@
         <v>24</v>
       </c>
       <c r="E162" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F162" t="s">
         <v>869</v>
@@ -6310,7 +6311,7 @@
         <v>24</v>
       </c>
       <c r="E163" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F163" t="s">
         <v>869</v>
@@ -6330,7 +6331,7 @@
         <v>24</v>
       </c>
       <c r="E164" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F164" t="s">
         <v>869</v>
@@ -6350,7 +6351,7 @@
         <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F165" t="s">
         <v>869</v>
@@ -6370,7 +6371,7 @@
         <v>24</v>
       </c>
       <c r="E166" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F166" t="s">
         <v>869</v>
@@ -6390,7 +6391,7 @@
         <v>24</v>
       </c>
       <c r="E167" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F167" t="s">
         <v>869</v>
@@ -6410,7 +6411,7 @@
         <v>24</v>
       </c>
       <c r="E168" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F168" t="s">
         <v>869</v>
@@ -6430,7 +6431,7 @@
         <v>24</v>
       </c>
       <c r="E169" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F169" t="s">
         <v>869</v>
@@ -6450,7 +6451,7 @@
         <v>24</v>
       </c>
       <c r="E170" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F170" t="s">
         <v>869</v>
@@ -6470,7 +6471,7 @@
         <v>24</v>
       </c>
       <c r="E171" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F171" t="s">
         <v>869</v>
@@ -6490,7 +6491,7 @@
         <v>24</v>
       </c>
       <c r="E172" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F172" t="s">
         <v>869</v>
@@ -6510,7 +6511,7 @@
         <v>24</v>
       </c>
       <c r="E173" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F173" t="s">
         <v>869</v>
@@ -6530,7 +6531,7 @@
         <v>24</v>
       </c>
       <c r="E174" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F174" t="s">
         <v>869</v>
@@ -6550,7 +6551,7 @@
         <v>24</v>
       </c>
       <c r="E175" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F175" t="s">
         <v>869</v>
@@ -6570,7 +6571,7 @@
         <v>24</v>
       </c>
       <c r="E176" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F176" t="s">
         <v>869</v>
@@ -6590,7 +6591,7 @@
         <v>24</v>
       </c>
       <c r="E177" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F177" t="s">
         <v>869</v>
@@ -6610,7 +6611,7 @@
         <v>24</v>
       </c>
       <c r="E178" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F178" t="s">
         <v>869</v>
@@ -6630,7 +6631,7 @@
         <v>24</v>
       </c>
       <c r="E179" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F179" t="s">
         <v>869</v>
@@ -6650,7 +6651,7 @@
         <v>24</v>
       </c>
       <c r="E180" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F180" t="s">
         <v>869</v>
@@ -6670,7 +6671,7 @@
         <v>24</v>
       </c>
       <c r="E181" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F181" t="s">
         <v>869</v>
@@ -6690,7 +6691,7 @@
         <v>24</v>
       </c>
       <c r="E182" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F182" t="s">
         <v>869</v>
@@ -6710,7 +6711,7 @@
         <v>24</v>
       </c>
       <c r="E183" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F183" t="s">
         <v>869</v>
@@ -6730,7 +6731,7 @@
         <v>24</v>
       </c>
       <c r="E184" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F184" t="s">
         <v>869</v>
@@ -6750,7 +6751,7 @@
         <v>24</v>
       </c>
       <c r="E185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F185" t="s">
         <v>869</v>
@@ -6770,7 +6771,7 @@
         <v>24</v>
       </c>
       <c r="E186" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F186" t="s">
         <v>869</v>
@@ -6790,7 +6791,7 @@
         <v>24</v>
       </c>
       <c r="E187" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F187" t="s">
         <v>869</v>
@@ -6810,7 +6811,7 @@
         <v>24</v>
       </c>
       <c r="E188" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F188" t="s">
         <v>869</v>
@@ -6830,7 +6831,7 @@
         <v>24</v>
       </c>
       <c r="E189" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F189" t="s">
         <v>869</v>
@@ -6850,7 +6851,7 @@
         <v>24</v>
       </c>
       <c r="E190" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F190" t="s">
         <v>869</v>
@@ -6870,7 +6871,7 @@
         <v>24</v>
       </c>
       <c r="E191" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F191" t="s">
         <v>869</v>
@@ -6890,7 +6891,7 @@
         <v>24</v>
       </c>
       <c r="E192" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F192" t="s">
         <v>869</v>
@@ -6910,7 +6911,7 @@
         <v>24</v>
       </c>
       <c r="E193" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F193" t="s">
         <v>869</v>
@@ -6930,7 +6931,7 @@
         <v>24</v>
       </c>
       <c r="E194" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F194" t="s">
         <v>869</v>
@@ -6950,7 +6951,7 @@
         <v>24</v>
       </c>
       <c r="E195" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F195" t="s">
         <v>869</v>
@@ -6970,7 +6971,7 @@
         <v>24</v>
       </c>
       <c r="E196" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F196" t="s">
         <v>869</v>
@@ -6990,7 +6991,7 @@
         <v>24</v>
       </c>
       <c r="E197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F197" t="s">
         <v>869</v>
@@ -7010,7 +7011,7 @@
         <v>24</v>
       </c>
       <c r="E198" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F198" t="s">
         <v>869</v>
@@ -7030,7 +7031,7 @@
         <v>24</v>
       </c>
       <c r="E199" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F199" t="s">
         <v>869</v>
@@ -7050,7 +7051,7 @@
         <v>24</v>
       </c>
       <c r="E200" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F200" t="s">
         <v>869</v>
@@ -7070,7 +7071,7 @@
         <v>24</v>
       </c>
       <c r="E201" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F201" t="s">
         <v>869</v>
@@ -7090,7 +7091,7 @@
         <v>24</v>
       </c>
       <c r="E202" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F202" t="s">
         <v>869</v>
@@ -7110,7 +7111,7 @@
         <v>24</v>
       </c>
       <c r="E203" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F203" t="s">
         <v>869</v>
@@ -7130,7 +7131,7 @@
         <v>24</v>
       </c>
       <c r="E204" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F204" t="s">
         <v>869</v>
@@ -7150,7 +7151,7 @@
         <v>24</v>
       </c>
       <c r="E205" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F205" t="s">
         <v>869</v>
@@ -7170,7 +7171,7 @@
         <v>24</v>
       </c>
       <c r="E206" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F206" t="s">
         <v>869</v>
@@ -7190,7 +7191,7 @@
         <v>24</v>
       </c>
       <c r="E207" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F207" t="s">
         <v>869</v>
@@ -7210,7 +7211,7 @@
         <v>24</v>
       </c>
       <c r="E208" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F208" t="s">
         <v>869</v>
@@ -7230,7 +7231,7 @@
         <v>24</v>
       </c>
       <c r="E209" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F209" t="s">
         <v>869</v>
@@ -7250,7 +7251,7 @@
         <v>24</v>
       </c>
       <c r="E210" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F210" t="s">
         <v>869</v>
@@ -7270,7 +7271,7 @@
         <v>24</v>
       </c>
       <c r="E211" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F211" t="s">
         <v>869</v>
@@ -7290,7 +7291,7 @@
         <v>24</v>
       </c>
       <c r="E212" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F212" t="s">
         <v>869</v>
@@ -7310,7 +7311,7 @@
         <v>24</v>
       </c>
       <c r="E213" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F213" t="s">
         <v>869</v>
@@ -7330,7 +7331,7 @@
         <v>24</v>
       </c>
       <c r="E214" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F214" t="s">
         <v>869</v>
@@ -7350,7 +7351,7 @@
         <v>24</v>
       </c>
       <c r="E215" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F215" t="s">
         <v>869</v>
@@ -7370,7 +7371,7 @@
         <v>24</v>
       </c>
       <c r="E216" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F216" t="s">
         <v>869</v>
@@ -7390,7 +7391,7 @@
         <v>24</v>
       </c>
       <c r="E217" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F217" t="s">
         <v>869</v>
@@ -7410,7 +7411,7 @@
         <v>24</v>
       </c>
       <c r="E218" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F218" t="s">
         <v>869</v>
@@ -7430,7 +7431,7 @@
         <v>24</v>
       </c>
       <c r="E219" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F219" t="s">
         <v>869</v>
@@ -7450,7 +7451,7 @@
         <v>24</v>
       </c>
       <c r="E220" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F220" t="s">
         <v>869</v>
@@ -7470,7 +7471,7 @@
         <v>24</v>
       </c>
       <c r="E221" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F221" t="s">
         <v>869</v>
@@ -7490,7 +7491,7 @@
         <v>24</v>
       </c>
       <c r="E222" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F222" t="s">
         <v>869</v>
@@ -7510,7 +7511,7 @@
         <v>24</v>
       </c>
       <c r="E223" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F223" t="s">
         <v>869</v>
@@ -7530,7 +7531,7 @@
         <v>24</v>
       </c>
       <c r="E224" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F224" t="s">
         <v>869</v>
@@ -7550,7 +7551,7 @@
         <v>24</v>
       </c>
       <c r="E225" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F225" t="s">
         <v>869</v>
@@ -7570,7 +7571,7 @@
         <v>24</v>
       </c>
       <c r="E226" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F226" t="s">
         <v>869</v>
@@ -7590,7 +7591,7 @@
         <v>24</v>
       </c>
       <c r="E227" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F227" t="s">
         <v>869</v>
@@ -7610,7 +7611,7 @@
         <v>24</v>
       </c>
       <c r="E228" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F228" t="s">
         <v>869</v>
@@ -7630,7 +7631,7 @@
         <v>24</v>
       </c>
       <c r="E229" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F229" t="s">
         <v>869</v>
@@ -7650,7 +7651,7 @@
         <v>24</v>
       </c>
       <c r="E230" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F230" t="s">
         <v>869</v>
@@ -7670,7 +7671,7 @@
         <v>24</v>
       </c>
       <c r="E231" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F231" t="s">
         <v>869</v>
@@ -7690,7 +7691,7 @@
         <v>24</v>
       </c>
       <c r="E232" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F232" t="s">
         <v>869</v>
@@ -7710,7 +7711,7 @@
         <v>24</v>
       </c>
       <c r="E233" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F233" t="s">
         <v>869</v>
@@ -7730,7 +7731,7 @@
         <v>24</v>
       </c>
       <c r="E234" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F234" t="s">
         <v>869</v>
@@ -7750,7 +7751,7 @@
         <v>24</v>
       </c>
       <c r="E235" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F235" t="s">
         <v>869</v>
@@ -7770,7 +7771,7 @@
         <v>24</v>
       </c>
       <c r="E236" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F236" t="s">
         <v>869</v>
@@ -7790,7 +7791,7 @@
         <v>24</v>
       </c>
       <c r="E237" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F237" t="s">
         <v>869</v>
@@ -7810,7 +7811,7 @@
         <v>24</v>
       </c>
       <c r="E238" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F238" t="s">
         <v>869</v>
@@ -7830,7 +7831,7 @@
         <v>24</v>
       </c>
       <c r="E239" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F239" t="s">
         <v>869</v>
@@ -7850,7 +7851,7 @@
         <v>24</v>
       </c>
       <c r="E240" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F240" t="s">
         <v>869</v>
@@ -7870,7 +7871,7 @@
         <v>24</v>
       </c>
       <c r="E241" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F241" t="s">
         <v>869</v>
@@ -7890,7 +7891,7 @@
         <v>24</v>
       </c>
       <c r="E242" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F242" t="s">
         <v>869</v>
@@ -7910,7 +7911,7 @@
         <v>24</v>
       </c>
       <c r="E243" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F243" t="s">
         <v>869</v>
@@ -7930,7 +7931,7 @@
         <v>24</v>
       </c>
       <c r="E244" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F244" t="s">
         <v>869</v>
@@ -7950,7 +7951,7 @@
         <v>24</v>
       </c>
       <c r="E245" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F245" t="s">
         <v>869</v>
@@ -7970,7 +7971,7 @@
         <v>24</v>
       </c>
       <c r="E246" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F246" t="s">
         <v>869</v>
@@ -7990,7 +7991,7 @@
         <v>24</v>
       </c>
       <c r="E247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F247" t="s">
         <v>869</v>
@@ -8010,7 +8011,7 @@
         <v>24</v>
       </c>
       <c r="E248" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F248" t="s">
         <v>869</v>
@@ -8030,7 +8031,7 @@
         <v>24</v>
       </c>
       <c r="E249" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F249" t="s">
         <v>869</v>
@@ -8050,7 +8051,7 @@
         <v>24</v>
       </c>
       <c r="E250" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F250" t="s">
         <v>869</v>
@@ -8070,7 +8071,7 @@
         <v>24</v>
       </c>
       <c r="E251" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F251" t="s">
         <v>869</v>
@@ -8090,7 +8091,7 @@
         <v>24</v>
       </c>
       <c r="E252" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F252" t="s">
         <v>869</v>
@@ -8110,7 +8111,7 @@
         <v>24</v>
       </c>
       <c r="E253" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F253" t="s">
         <v>869</v>
@@ -8130,7 +8131,7 @@
         <v>24</v>
       </c>
       <c r="E254" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F254" t="s">
         <v>869</v>
@@ -8150,7 +8151,7 @@
         <v>24</v>
       </c>
       <c r="E255" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F255" t="s">
         <v>869</v>
@@ -8170,7 +8171,7 @@
         <v>24</v>
       </c>
       <c r="E256" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F256" t="s">
         <v>869</v>
@@ -8190,7 +8191,7 @@
         <v>24</v>
       </c>
       <c r="E257" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F257" t="s">
         <v>869</v>
@@ -8210,7 +8211,7 @@
         <v>24</v>
       </c>
       <c r="E258" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F258" t="s">
         <v>869</v>
@@ -8230,7 +8231,7 @@
         <v>24</v>
       </c>
       <c r="E259" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F259" t="s">
         <v>869</v>
@@ -8250,7 +8251,7 @@
         <v>24</v>
       </c>
       <c r="E260" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F260" t="s">
         <v>869</v>
@@ -8270,7 +8271,7 @@
         <v>24</v>
       </c>
       <c r="E261" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F261" t="s">
         <v>869</v>
@@ -8290,7 +8291,7 @@
         <v>24</v>
       </c>
       <c r="E262" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F262" t="s">
         <v>869</v>
@@ -8310,7 +8311,7 @@
         <v>24</v>
       </c>
       <c r="E263" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F263" t="s">
         <v>869</v>
@@ -8330,7 +8331,7 @@
         <v>24</v>
       </c>
       <c r="E264" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F264" t="s">
         <v>869</v>
@@ -8350,7 +8351,7 @@
         <v>24</v>
       </c>
       <c r="E265" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F265" t="s">
         <v>869</v>
@@ -8370,7 +8371,7 @@
         <v>24</v>
       </c>
       <c r="E266" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F266" t="s">
         <v>869</v>
@@ -8390,7 +8391,7 @@
         <v>24</v>
       </c>
       <c r="E267" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F267" t="s">
         <v>869</v>
@@ -8410,7 +8411,7 @@
         <v>24</v>
       </c>
       <c r="E268" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F268" t="s">
         <v>869</v>
@@ -8430,7 +8431,7 @@
         <v>24</v>
       </c>
       <c r="E269" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F269" t="s">
         <v>869</v>
@@ -8450,7 +8451,7 @@
         <v>24</v>
       </c>
       <c r="E270" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F270" t="s">
         <v>869</v>
@@ -8470,7 +8471,7 @@
         <v>24</v>
       </c>
       <c r="E271" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F271" t="s">
         <v>869</v>
@@ -8490,7 +8491,7 @@
         <v>24</v>
       </c>
       <c r="E272" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F272" t="s">
         <v>869</v>
@@ -8510,7 +8511,7 @@
         <v>24</v>
       </c>
       <c r="E273" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F273" t="s">
         <v>869</v>
@@ -8530,7 +8531,7 @@
         <v>24</v>
       </c>
       <c r="E274" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F274" t="s">
         <v>869</v>
@@ -8550,7 +8551,7 @@
         <v>24</v>
       </c>
       <c r="E275" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F275" t="s">
         <v>869</v>
@@ -8570,7 +8571,7 @@
         <v>24</v>
       </c>
       <c r="E276" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F276" t="s">
         <v>869</v>
@@ -8590,7 +8591,7 @@
         <v>24</v>
       </c>
       <c r="E277" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F277" t="s">
         <v>869</v>
@@ -8610,7 +8611,7 @@
         <v>24</v>
       </c>
       <c r="E278" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F278" t="s">
         <v>869</v>
@@ -8630,7 +8631,7 @@
         <v>24</v>
       </c>
       <c r="E279" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F279" t="s">
         <v>869</v>
@@ -8650,7 +8651,7 @@
         <v>24</v>
       </c>
       <c r="E280" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F280" t="s">
         <v>869</v>
@@ -8670,7 +8671,7 @@
         <v>24</v>
       </c>
       <c r="E281" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F281" t="s">
         <v>869</v>
@@ -8690,7 +8691,7 @@
         <v>24</v>
       </c>
       <c r="E282" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F282" t="s">
         <v>869</v>
@@ -8710,7 +8711,7 @@
         <v>24</v>
       </c>
       <c r="E283" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F283" t="s">
         <v>869</v>
@@ -8730,7 +8731,7 @@
         <v>24</v>
       </c>
       <c r="E284" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F284" t="s">
         <v>869</v>
@@ -8750,7 +8751,7 @@
         <v>24</v>
       </c>
       <c r="E285" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F285" t="s">
         <v>869</v>
@@ -8770,7 +8771,7 @@
         <v>24</v>
       </c>
       <c r="E286" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F286" t="s">
         <v>869</v>
@@ -8790,7 +8791,7 @@
         <v>24</v>
       </c>
       <c r="E287" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F287" t="s">
         <v>869</v>
@@ -8810,7 +8811,7 @@
         <v>24</v>
       </c>
       <c r="E288" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F288" t="s">
         <v>869</v>
@@ -8830,7 +8831,7 @@
         <v>24</v>
       </c>
       <c r="E289" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F289" t="s">
         <v>869</v>
@@ -8850,7 +8851,7 @@
         <v>24</v>
       </c>
       <c r="E290" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F290" t="s">
         <v>869</v>
@@ -8870,7 +8871,7 @@
         <v>24</v>
       </c>
       <c r="E291" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F291" t="s">
         <v>869</v>
@@ -8890,7 +8891,7 @@
         <v>24</v>
       </c>
       <c r="E292" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F292" t="s">
         <v>869</v>
@@ -8910,7 +8911,7 @@
         <v>24</v>
       </c>
       <c r="E293" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F293" t="s">
         <v>869</v>
@@ -8930,7 +8931,7 @@
         <v>24</v>
       </c>
       <c r="E294" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F294" t="s">
         <v>869</v>
@@ -8950,7 +8951,7 @@
         <v>24</v>
       </c>
       <c r="E295" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F295" t="s">
         <v>869</v>
@@ -8970,7 +8971,7 @@
         <v>24</v>
       </c>
       <c r="E296" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F296" t="s">
         <v>869</v>
@@ -8990,7 +8991,7 @@
         <v>24</v>
       </c>
       <c r="E297" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F297" t="s">
         <v>869</v>
@@ -9010,7 +9011,7 @@
         <v>24</v>
       </c>
       <c r="E298" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F298" t="s">
         <v>869</v>
@@ -9030,7 +9031,7 @@
         <v>24</v>
       </c>
       <c r="E299" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F299" t="s">
         <v>869</v>
@@ -9050,7 +9051,7 @@
         <v>24</v>
       </c>
       <c r="E300" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F300" t="s">
         <v>869</v>
@@ -9070,7 +9071,7 @@
         <v>24</v>
       </c>
       <c r="E301" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F301" t="s">
         <v>869</v>
@@ -9090,7 +9091,7 @@
         <v>24</v>
       </c>
       <c r="E302" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F302" t="s">
         <v>869</v>
@@ -9110,7 +9111,7 @@
         <v>24</v>
       </c>
       <c r="E303" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F303" t="s">
         <v>869</v>
@@ -9130,7 +9131,7 @@
         <v>24</v>
       </c>
       <c r="E304" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F304" t="s">
         <v>869</v>
@@ -9150,7 +9151,7 @@
         <v>24</v>
       </c>
       <c r="E305" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F305" t="s">
         <v>869</v>
@@ -9170,7 +9171,7 @@
         <v>24</v>
       </c>
       <c r="E306" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F306" t="s">
         <v>869</v>
@@ -9190,7 +9191,7 @@
         <v>24</v>
       </c>
       <c r="E307" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F307" t="s">
         <v>869</v>
@@ -9210,7 +9211,7 @@
         <v>24</v>
       </c>
       <c r="E308" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F308" t="s">
         <v>869</v>
@@ -9230,7 +9231,7 @@
         <v>24</v>
       </c>
       <c r="E309" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F309" t="s">
         <v>869</v>
@@ -9250,7 +9251,7 @@
         <v>24</v>
       </c>
       <c r="E310" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F310" t="s">
         <v>869</v>
@@ -9270,7 +9271,7 @@
         <v>24</v>
       </c>
       <c r="E311" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F311" t="s">
         <v>869</v>
@@ -9290,7 +9291,7 @@
         <v>24</v>
       </c>
       <c r="E312" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F312" t="s">
         <v>869</v>
@@ -9310,7 +9311,7 @@
         <v>24</v>
       </c>
       <c r="E313" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F313" t="s">
         <v>869</v>
@@ -9330,7 +9331,7 @@
         <v>24</v>
       </c>
       <c r="E314" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F314" t="s">
         <v>869</v>
@@ -9350,7 +9351,7 @@
         <v>24</v>
       </c>
       <c r="E315" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F315" t="s">
         <v>869</v>
@@ -9370,7 +9371,7 @@
         <v>24</v>
       </c>
       <c r="E316" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F316" t="s">
         <v>869</v>
@@ -9390,7 +9391,7 @@
         <v>24</v>
       </c>
       <c r="E317" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F317" t="s">
         <v>869</v>
@@ -9410,7 +9411,7 @@
         <v>24</v>
       </c>
       <c r="E318" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F318" t="s">
         <v>869</v>
@@ -9430,7 +9431,7 @@
         <v>24</v>
       </c>
       <c r="E319" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F319" t="s">
         <v>869</v>
@@ -9450,7 +9451,7 @@
         <v>24</v>
       </c>
       <c r="E320" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F320" t="s">
         <v>869</v>
@@ -9470,7 +9471,7 @@
         <v>24</v>
       </c>
       <c r="E321" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F321" t="s">
         <v>869</v>
@@ -9490,7 +9491,7 @@
         <v>24</v>
       </c>
       <c r="E322" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F322" t="s">
         <v>869</v>
@@ -9510,7 +9511,7 @@
         <v>24</v>
       </c>
       <c r="E323" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F323" t="s">
         <v>869</v>
@@ -9530,7 +9531,7 @@
         <v>24</v>
       </c>
       <c r="E324" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F324" t="s">
         <v>869</v>
@@ -9550,7 +9551,7 @@
         <v>24</v>
       </c>
       <c r="E325" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F325" t="s">
         <v>869</v>
@@ -9570,7 +9571,7 @@
         <v>24</v>
       </c>
       <c r="E326" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F326" t="s">
         <v>869</v>
@@ -9590,7 +9591,7 @@
         <v>24</v>
       </c>
       <c r="E327" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F327" t="s">
         <v>869</v>
@@ -9610,7 +9611,7 @@
         <v>24</v>
       </c>
       <c r="E328" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F328" t="s">
         <v>869</v>
@@ -9630,7 +9631,7 @@
         <v>24</v>
       </c>
       <c r="E329" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F329" t="s">
         <v>869</v>
@@ -9650,7 +9651,7 @@
         <v>24</v>
       </c>
       <c r="E330" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F330" t="s">
         <v>869</v>
@@ -9670,7 +9671,7 @@
         <v>24</v>
       </c>
       <c r="E331" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F331" t="s">
         <v>869</v>
@@ -9690,7 +9691,7 @@
         <v>24</v>
       </c>
       <c r="E332" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F332" t="s">
         <v>869</v>
@@ -9710,7 +9711,7 @@
         <v>24</v>
       </c>
       <c r="E333" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F333" t="s">
         <v>869</v>
@@ -9730,7 +9731,7 @@
         <v>24</v>
       </c>
       <c r="E334" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F334" t="s">
         <v>869</v>
@@ -9750,7 +9751,7 @@
         <v>24</v>
       </c>
       <c r="E335" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F335" t="s">
         <v>869</v>
@@ -9770,7 +9771,7 @@
         <v>24</v>
       </c>
       <c r="E336" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F336" t="s">
         <v>869</v>
@@ -9790,7 +9791,7 @@
         <v>24</v>
       </c>
       <c r="E337" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F337" t="s">
         <v>869</v>
@@ -9810,7 +9811,7 @@
         <v>24</v>
       </c>
       <c r="E338" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F338" t="s">
         <v>869</v>
@@ -9830,7 +9831,7 @@
         <v>24</v>
       </c>
       <c r="E339" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F339" t="s">
         <v>869</v>
@@ -9850,7 +9851,7 @@
         <v>24</v>
       </c>
       <c r="E340" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F340" t="s">
         <v>869</v>
@@ -9870,7 +9871,7 @@
         <v>24</v>
       </c>
       <c r="E341" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F341" t="s">
         <v>869</v>
@@ -9890,7 +9891,7 @@
         <v>24</v>
       </c>
       <c r="E342" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F342" t="s">
         <v>869</v>
@@ -9910,7 +9911,7 @@
         <v>24</v>
       </c>
       <c r="E343" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F343" t="s">
         <v>869</v>
@@ -9930,7 +9931,7 @@
         <v>24</v>
       </c>
       <c r="E344" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F344" t="s">
         <v>869</v>
@@ -9950,7 +9951,7 @@
         <v>24</v>
       </c>
       <c r="E345" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F345" t="s">
         <v>869</v>
@@ -9970,7 +9971,7 @@
         <v>24</v>
       </c>
       <c r="E346" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F346" t="s">
         <v>869</v>
@@ -9990,7 +9991,7 @@
         <v>24</v>
       </c>
       <c r="E347" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F347" t="s">
         <v>869</v>
@@ -10010,7 +10011,7 @@
         <v>24</v>
       </c>
       <c r="E348" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F348" t="s">
         <v>869</v>
@@ -10030,7 +10031,7 @@
         <v>24</v>
       </c>
       <c r="E349" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F349" t="s">
         <v>869</v>
@@ -10050,7 +10051,7 @@
         <v>24</v>
       </c>
       <c r="E350" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F350" t="s">
         <v>869</v>
@@ -10070,7 +10071,7 @@
         <v>24</v>
       </c>
       <c r="E351" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F351" t="s">
         <v>869</v>
@@ -10090,7 +10091,7 @@
         <v>24</v>
       </c>
       <c r="E352" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F352" t="s">
         <v>869</v>
@@ -10110,7 +10111,7 @@
         <v>24</v>
       </c>
       <c r="E353" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F353" t="s">
         <v>869</v>
@@ -10130,7 +10131,7 @@
         <v>24</v>
       </c>
       <c r="E354" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F354" t="s">
         <v>869</v>
@@ -10150,7 +10151,7 @@
         <v>24</v>
       </c>
       <c r="E355" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F355" t="s">
         <v>869</v>
@@ -10170,7 +10171,7 @@
         <v>24</v>
       </c>
       <c r="E356" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F356" t="s">
         <v>869</v>
@@ -10190,7 +10191,7 @@
         <v>24</v>
       </c>
       <c r="E357" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F357" t="s">
         <v>869</v>
@@ -10210,7 +10211,7 @@
         <v>24</v>
       </c>
       <c r="E358" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F358" t="s">
         <v>869</v>
@@ -10230,7 +10231,7 @@
         <v>24</v>
       </c>
       <c r="E359" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F359" t="s">
         <v>869</v>
@@ -10250,7 +10251,7 @@
         <v>24</v>
       </c>
       <c r="E360" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F360" t="s">
         <v>869</v>
@@ -10270,7 +10271,7 @@
         <v>24</v>
       </c>
       <c r="E361" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F361" t="s">
         <v>869</v>
@@ -10290,7 +10291,7 @@
         <v>24</v>
       </c>
       <c r="E362" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F362" t="s">
         <v>869</v>
@@ -10310,7 +10311,7 @@
         <v>24</v>
       </c>
       <c r="E363" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F363" t="s">
         <v>869</v>
@@ -10330,7 +10331,7 @@
         <v>24</v>
       </c>
       <c r="E364" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F364" t="s">
         <v>869</v>
@@ -10350,7 +10351,7 @@
         <v>24</v>
       </c>
       <c r="E365" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F365" t="s">
         <v>869</v>
@@ -10370,7 +10371,7 @@
         <v>24</v>
       </c>
       <c r="E366" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F366" t="s">
         <v>869</v>
@@ -10390,7 +10391,7 @@
         <v>24</v>
       </c>
       <c r="E367" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F367" t="s">
         <v>869</v>
@@ -10410,7 +10411,7 @@
         <v>24</v>
       </c>
       <c r="E368" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F368" t="s">
         <v>869</v>
@@ -10430,7 +10431,7 @@
         <v>24</v>
       </c>
       <c r="E369" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F369" t="s">
         <v>869</v>
@@ -10450,7 +10451,7 @@
         <v>24</v>
       </c>
       <c r="E370" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F370" t="s">
         <v>869</v>
@@ -10470,7 +10471,7 @@
         <v>24</v>
       </c>
       <c r="E371" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F371" t="s">
         <v>869</v>
@@ -10490,7 +10491,7 @@
         <v>24</v>
       </c>
       <c r="E372" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F372" t="s">
         <v>869</v>
@@ -10510,7 +10511,7 @@
         <v>24</v>
       </c>
       <c r="E373" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F373" t="s">
         <v>869</v>
@@ -10530,7 +10531,7 @@
         <v>24</v>
       </c>
       <c r="E374" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F374" t="s">
         <v>869</v>
@@ -10550,7 +10551,7 @@
         <v>24</v>
       </c>
       <c r="E375" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F375" t="s">
         <v>869</v>
@@ -10570,7 +10571,7 @@
         <v>24</v>
       </c>
       <c r="E376" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F376" t="s">
         <v>869</v>
@@ -10590,7 +10591,7 @@
         <v>24</v>
       </c>
       <c r="E377" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F377" t="s">
         <v>869</v>
@@ -10610,7 +10611,7 @@
         <v>24</v>
       </c>
       <c r="E378" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F378" t="s">
         <v>869</v>
@@ -10630,7 +10631,7 @@
         <v>24</v>
       </c>
       <c r="E379" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F379" t="s">
         <v>869</v>
@@ -10650,7 +10651,7 @@
         <v>24</v>
       </c>
       <c r="E380" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F380" t="s">
         <v>869</v>
@@ -10670,7 +10671,7 @@
         <v>24</v>
       </c>
       <c r="E381" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F381" t="s">
         <v>869</v>
@@ -10690,7 +10691,7 @@
         <v>24</v>
       </c>
       <c r="E382" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F382" t="s">
         <v>869</v>
@@ -10710,7 +10711,7 @@
         <v>24</v>
       </c>
       <c r="E383" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F383" t="s">
         <v>869</v>
@@ -10730,7 +10731,7 @@
         <v>24</v>
       </c>
       <c r="E384" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F384" t="s">
         <v>869</v>
@@ -10750,7 +10751,7 @@
         <v>24</v>
       </c>
       <c r="E385" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F385" t="s">
         <v>869</v>
@@ -10770,7 +10771,7 @@
         <v>393</v>
       </c>
       <c r="E386" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F386" t="s">
         <v>872</v>
@@ -10790,7 +10791,7 @@
         <v>393</v>
       </c>
       <c r="E387" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F387" t="s">
         <v>872</v>
@@ -10810,7 +10811,7 @@
         <v>393</v>
       </c>
       <c r="E388" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F388" t="s">
         <v>872</v>
@@ -10830,7 +10831,7 @@
         <v>393</v>
       </c>
       <c r="E389" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F389" t="s">
         <v>872</v>
@@ -10850,7 +10851,7 @@
         <v>393</v>
       </c>
       <c r="E390" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F390" t="s">
         <v>872</v>
@@ -10870,7 +10871,7 @@
         <v>393</v>
       </c>
       <c r="E391" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F391" t="s">
         <v>872</v>
@@ -10890,7 +10891,7 @@
         <v>393</v>
       </c>
       <c r="E392" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F392" t="s">
         <v>872</v>
@@ -10910,7 +10911,7 @@
         <v>393</v>
       </c>
       <c r="E393" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F393" t="s">
         <v>872</v>
@@ -10930,7 +10931,7 @@
         <v>393</v>
       </c>
       <c r="E394" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F394" t="s">
         <v>872</v>
@@ -10950,7 +10951,7 @@
         <v>393</v>
       </c>
       <c r="E395" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F395" t="s">
         <v>872</v>
@@ -10970,7 +10971,7 @@
         <v>393</v>
       </c>
       <c r="E396" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F396" t="s">
         <v>872</v>
@@ -10990,7 +10991,7 @@
         <v>393</v>
       </c>
       <c r="E397" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F397" t="s">
         <v>872</v>
@@ -11010,7 +11011,7 @@
         <v>393</v>
       </c>
       <c r="E398" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F398" t="s">
         <v>872</v>
@@ -11030,7 +11031,7 @@
         <v>393</v>
       </c>
       <c r="E399" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F399" t="s">
         <v>872</v>
@@ -11050,7 +11051,7 @@
         <v>393</v>
       </c>
       <c r="E400" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F400" t="s">
         <v>872</v>
@@ -11070,7 +11071,7 @@
         <v>393</v>
       </c>
       <c r="E401" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F401" t="s">
         <v>872</v>
@@ -11090,7 +11091,7 @@
         <v>393</v>
       </c>
       <c r="E402" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F402" t="s">
         <v>871</v>
@@ -11110,7 +11111,7 @@
         <v>393</v>
       </c>
       <c r="E403" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F403" t="s">
         <v>871</v>
@@ -11130,7 +11131,7 @@
         <v>393</v>
       </c>
       <c r="E404" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F404" t="s">
         <v>871</v>
@@ -11150,7 +11151,7 @@
         <v>393</v>
       </c>
       <c r="E405" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F405" t="s">
         <v>871</v>
@@ -11170,7 +11171,7 @@
         <v>393</v>
       </c>
       <c r="E406" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F406" t="s">
         <v>871</v>
@@ -11190,7 +11191,7 @@
         <v>393</v>
       </c>
       <c r="E407" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F407" t="s">
         <v>871</v>
@@ -11210,7 +11211,7 @@
         <v>393</v>
       </c>
       <c r="E408" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F408" t="s">
         <v>871</v>
@@ -11230,7 +11231,7 @@
         <v>393</v>
       </c>
       <c r="E409" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F409" t="s">
         <v>871</v>
@@ -11250,7 +11251,7 @@
         <v>393</v>
       </c>
       <c r="E410" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F410" t="s">
         <v>871</v>
@@ -11270,7 +11271,7 @@
         <v>393</v>
       </c>
       <c r="E411" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F411" t="s">
         <v>871</v>
@@ -11290,7 +11291,7 @@
         <v>393</v>
       </c>
       <c r="E412" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F412" t="s">
         <v>871</v>
@@ -11310,7 +11311,7 @@
         <v>393</v>
       </c>
       <c r="E413" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F413" t="s">
         <v>871</v>
@@ -11330,7 +11331,7 @@
         <v>393</v>
       </c>
       <c r="E414" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F414" t="s">
         <v>871</v>
@@ -11350,7 +11351,7 @@
         <v>393</v>
       </c>
       <c r="E415" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F415" t="s">
         <v>871</v>
@@ -11370,7 +11371,7 @@
         <v>393</v>
       </c>
       <c r="E416" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F416" t="s">
         <v>871</v>
@@ -11390,7 +11391,7 @@
         <v>393</v>
       </c>
       <c r="E417" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F417" t="s">
         <v>871</v>
@@ -11410,7 +11411,7 @@
         <v>393</v>
       </c>
       <c r="E418" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F418" t="s">
         <v>871</v>
@@ -11430,7 +11431,7 @@
         <v>393</v>
       </c>
       <c r="E419" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F419" t="s">
         <v>871</v>
@@ -11450,7 +11451,7 @@
         <v>393</v>
       </c>
       <c r="E420" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F420" t="s">
         <v>871</v>
@@ -11470,7 +11471,7 @@
         <v>393</v>
       </c>
       <c r="E421" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F421" t="s">
         <v>871</v>
@@ -11490,7 +11491,7 @@
         <v>393</v>
       </c>
       <c r="E422" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F422" t="s">
         <v>871</v>
@@ -11510,7 +11511,7 @@
         <v>393</v>
       </c>
       <c r="E423" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F423" t="s">
         <v>871</v>
@@ -11530,7 +11531,7 @@
         <v>393</v>
       </c>
       <c r="E424" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F424" t="s">
         <v>871</v>
@@ -11550,7 +11551,7 @@
         <v>393</v>
       </c>
       <c r="E425" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F425" t="s">
         <v>871</v>
@@ -11570,7 +11571,7 @@
         <v>393</v>
       </c>
       <c r="E426" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F426" t="s">
         <v>871</v>
@@ -11590,7 +11591,7 @@
         <v>393</v>
       </c>
       <c r="E427" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F427" t="s">
         <v>871</v>
@@ -11610,7 +11611,7 @@
         <v>393</v>
       </c>
       <c r="E428" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F428" t="s">
         <v>871</v>
@@ -11630,7 +11631,7 @@
         <v>393</v>
       </c>
       <c r="E429" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F429" t="s">
         <v>871</v>
@@ -11650,7 +11651,7 @@
         <v>393</v>
       </c>
       <c r="E430" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F430" t="s">
         <v>871</v>
@@ -11670,7 +11671,7 @@
         <v>393</v>
       </c>
       <c r="E431" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F431" t="s">
         <v>871</v>
@@ -11690,7 +11691,7 @@
         <v>393</v>
       </c>
       <c r="E432" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F432" t="s">
         <v>871</v>
@@ -11710,7 +11711,7 @@
         <v>393</v>
       </c>
       <c r="E433" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F433" t="s">
         <v>871</v>
@@ -11730,7 +11731,7 @@
         <v>393</v>
       </c>
       <c r="E434" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F434" t="s">
         <v>871</v>
@@ -11750,7 +11751,7 @@
         <v>393</v>
       </c>
       <c r="E435" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F435" t="s">
         <v>871</v>
@@ -11770,7 +11771,7 @@
         <v>393</v>
       </c>
       <c r="E436" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F436" t="s">
         <v>871</v>
@@ -11790,7 +11791,7 @@
         <v>393</v>
       </c>
       <c r="E437" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F437" t="s">
         <v>871</v>
@@ -11810,7 +11811,7 @@
         <v>393</v>
       </c>
       <c r="E438" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F438" t="s">
         <v>871</v>
@@ -11830,7 +11831,7 @@
         <v>393</v>
       </c>
       <c r="E439" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F439" t="s">
         <v>871</v>
@@ -11850,7 +11851,7 @@
         <v>393</v>
       </c>
       <c r="E440" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F440" t="s">
         <v>871</v>
@@ -11870,7 +11871,7 @@
         <v>393</v>
       </c>
       <c r="E441" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F441" t="s">
         <v>871</v>
@@ -11890,7 +11891,7 @@
         <v>393</v>
       </c>
       <c r="E442" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F442" t="s">
         <v>871</v>
@@ -11910,7 +11911,7 @@
         <v>393</v>
       </c>
       <c r="E443" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F443" t="s">
         <v>871</v>
@@ -11930,7 +11931,7 @@
         <v>393</v>
       </c>
       <c r="E444" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F444" t="s">
         <v>871</v>
@@ -11950,7 +11951,7 @@
         <v>393</v>
       </c>
       <c r="E445" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F445" t="s">
         <v>871</v>
@@ -11970,7 +11971,7 @@
         <v>393</v>
       </c>
       <c r="E446" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F446" t="s">
         <v>871</v>
@@ -11990,7 +11991,7 @@
         <v>393</v>
       </c>
       <c r="E447" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F447" t="s">
         <v>871</v>
@@ -12010,7 +12011,7 @@
         <v>393</v>
       </c>
       <c r="E448" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F448" t="s">
         <v>871</v>
@@ -12030,7 +12031,7 @@
         <v>393</v>
       </c>
       <c r="E449" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F449" t="s">
         <v>871</v>
@@ -12050,7 +12051,7 @@
         <v>393</v>
       </c>
       <c r="E450" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F450" t="s">
         <v>871</v>
@@ -12070,7 +12071,7 @@
         <v>393</v>
       </c>
       <c r="E451" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F451" t="s">
         <v>871</v>
@@ -12090,7 +12091,7 @@
         <v>393</v>
       </c>
       <c r="E452" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F452" t="s">
         <v>871</v>
@@ -12110,7 +12111,7 @@
         <v>393</v>
       </c>
       <c r="E453" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F453" t="s">
         <v>871</v>
@@ -12130,7 +12131,7 @@
         <v>393</v>
       </c>
       <c r="E454" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F454" t="s">
         <v>871</v>
@@ -12150,7 +12151,7 @@
         <v>393</v>
       </c>
       <c r="E455" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F455" t="s">
         <v>871</v>
@@ -12170,7 +12171,7 @@
         <v>393</v>
       </c>
       <c r="E456" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F456" t="s">
         <v>871</v>
@@ -12190,7 +12191,7 @@
         <v>393</v>
       </c>
       <c r="E457" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F457" t="s">
         <v>871</v>
@@ -12210,7 +12211,7 @@
         <v>393</v>
       </c>
       <c r="E458" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F458" t="s">
         <v>871</v>
@@ -12230,7 +12231,7 @@
         <v>393</v>
       </c>
       <c r="E459" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F459" t="s">
         <v>871</v>
@@ -12250,7 +12251,7 @@
         <v>393</v>
       </c>
       <c r="E460" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F460" t="s">
         <v>871</v>
@@ -12270,7 +12271,7 @@
         <v>393</v>
       </c>
       <c r="E461" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F461" t="s">
         <v>871</v>
@@ -12290,7 +12291,7 @@
         <v>393</v>
       </c>
       <c r="E462" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F462" t="s">
         <v>871</v>
@@ -12310,7 +12311,7 @@
         <v>393</v>
       </c>
       <c r="E463" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F463" t="s">
         <v>871</v>
@@ -12330,7 +12331,7 @@
         <v>393</v>
       </c>
       <c r="E464" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F464" t="s">
         <v>871</v>
@@ -12350,7 +12351,7 @@
         <v>393</v>
       </c>
       <c r="E465" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F465" t="s">
         <v>871</v>
@@ -12370,7 +12371,7 @@
         <v>393</v>
       </c>
       <c r="E466" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F466" t="s">
         <v>871</v>
@@ -12390,7 +12391,7 @@
         <v>393</v>
       </c>
       <c r="E467" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F467" t="s">
         <v>871</v>
@@ -12410,7 +12411,7 @@
         <v>393</v>
       </c>
       <c r="E468" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F468" t="s">
         <v>871</v>
@@ -12430,7 +12431,7 @@
         <v>393</v>
       </c>
       <c r="E469" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F469" t="s">
         <v>871</v>
@@ -12450,7 +12451,7 @@
         <v>393</v>
       </c>
       <c r="E470" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F470" t="s">
         <v>871</v>
@@ -12470,7 +12471,7 @@
         <v>393</v>
       </c>
       <c r="E471" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F471" t="s">
         <v>871</v>
@@ -12490,7 +12491,7 @@
         <v>393</v>
       </c>
       <c r="E472" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F472" t="s">
         <v>871</v>
@@ -12510,7 +12511,7 @@
         <v>393</v>
       </c>
       <c r="E473" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F473" t="s">
         <v>871</v>
@@ -12530,7 +12531,7 @@
         <v>393</v>
       </c>
       <c r="E474" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F474" t="s">
         <v>871</v>
@@ -12550,7 +12551,7 @@
         <v>393</v>
       </c>
       <c r="E475" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F475" t="s">
         <v>871</v>
@@ -12570,7 +12571,7 @@
         <v>393</v>
       </c>
       <c r="E476" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F476" t="s">
         <v>871</v>
@@ -12590,7 +12591,7 @@
         <v>393</v>
       </c>
       <c r="E477" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F477" t="s">
         <v>871</v>
@@ -12610,7 +12611,7 @@
         <v>393</v>
       </c>
       <c r="E478" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F478" t="s">
         <v>871</v>
@@ -12630,7 +12631,7 @@
         <v>393</v>
       </c>
       <c r="E479" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F479" t="s">
         <v>871</v>
@@ -12650,7 +12651,7 @@
         <v>393</v>
       </c>
       <c r="E480" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F480" t="s">
         <v>871</v>
@@ -12670,7 +12671,7 @@
         <v>393</v>
       </c>
       <c r="E481" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F481" t="s">
         <v>871</v>
@@ -12690,7 +12691,7 @@
         <v>393</v>
       </c>
       <c r="E482" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F482" t="s">
         <v>871</v>
@@ -12710,7 +12711,7 @@
         <v>393</v>
       </c>
       <c r="E483" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F483" t="s">
         <v>871</v>
@@ -12730,7 +12731,7 @@
         <v>393</v>
       </c>
       <c r="E484" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F484" t="s">
         <v>871</v>
@@ -12750,7 +12751,7 @@
         <v>393</v>
       </c>
       <c r="E485" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F485" t="s">
         <v>871</v>
@@ -12770,7 +12771,7 @@
         <v>393</v>
       </c>
       <c r="E486" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F486" t="s">
         <v>871</v>
@@ -12790,7 +12791,7 @@
         <v>393</v>
       </c>
       <c r="E487" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F487" t="s">
         <v>871</v>
@@ -12810,7 +12811,7 @@
         <v>393</v>
       </c>
       <c r="E488" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F488" t="s">
         <v>871</v>
@@ -12830,7 +12831,7 @@
         <v>393</v>
       </c>
       <c r="E489" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F489" t="s">
         <v>871</v>
@@ -12850,7 +12851,7 @@
         <v>393</v>
       </c>
       <c r="E490" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F490" t="s">
         <v>871</v>
@@ -12870,7 +12871,7 @@
         <v>393</v>
       </c>
       <c r="E491" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F491" t="s">
         <v>871</v>
@@ -12890,7 +12891,7 @@
         <v>393</v>
       </c>
       <c r="E492" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F492" t="s">
         <v>871</v>
@@ -12910,7 +12911,7 @@
         <v>393</v>
       </c>
       <c r="E493" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F493" t="s">
         <v>871</v>
@@ -12930,7 +12931,7 @@
         <v>393</v>
       </c>
       <c r="E494" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F494" t="s">
         <v>871</v>
@@ -12950,7 +12951,7 @@
         <v>393</v>
       </c>
       <c r="E495" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F495" t="s">
         <v>871</v>
@@ -12970,7 +12971,7 @@
         <v>393</v>
       </c>
       <c r="E496" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F496" t="s">
         <v>871</v>
@@ -12990,7 +12991,7 @@
         <v>393</v>
       </c>
       <c r="E497" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F497" t="s">
         <v>871</v>
@@ -13010,7 +13011,7 @@
         <v>393</v>
       </c>
       <c r="E498" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F498" t="s">
         <v>871</v>
@@ -13030,7 +13031,7 @@
         <v>393</v>
       </c>
       <c r="E499" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F499" t="s">
         <v>871</v>
@@ -13050,7 +13051,7 @@
         <v>393</v>
       </c>
       <c r="E500" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F500" t="s">
         <v>871</v>
@@ -13070,7 +13071,7 @@
         <v>393</v>
       </c>
       <c r="E501" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F501" t="s">
         <v>871</v>
@@ -13090,7 +13091,7 @@
         <v>393</v>
       </c>
       <c r="E502" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F502" t="s">
         <v>871</v>
@@ -13110,7 +13111,7 @@
         <v>393</v>
       </c>
       <c r="E503" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F503" t="s">
         <v>871</v>
@@ -13130,7 +13131,7 @@
         <v>393</v>
       </c>
       <c r="E504" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F504" t="s">
         <v>871</v>
@@ -13150,7 +13151,7 @@
         <v>393</v>
       </c>
       <c r="E505" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F505" t="s">
         <v>871</v>
@@ -13170,7 +13171,7 @@
         <v>393</v>
       </c>
       <c r="E506" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F506" t="s">
         <v>871</v>
@@ -13190,7 +13191,7 @@
         <v>393</v>
       </c>
       <c r="E507" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F507" t="s">
         <v>871</v>
@@ -13210,7 +13211,7 @@
         <v>393</v>
       </c>
       <c r="E508" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F508" t="s">
         <v>871</v>
@@ -13230,7 +13231,7 @@
         <v>393</v>
       </c>
       <c r="E509" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F509" t="s">
         <v>871</v>
@@ -13250,7 +13251,7 @@
         <v>393</v>
       </c>
       <c r="E510" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F510" t="s">
         <v>871</v>
@@ -13270,7 +13271,7 @@
         <v>393</v>
       </c>
       <c r="E511" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F511" t="s">
         <v>871</v>
@@ -13290,7 +13291,7 @@
         <v>393</v>
       </c>
       <c r="E512" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F512" t="s">
         <v>871</v>
@@ -13310,7 +13311,7 @@
         <v>393</v>
       </c>
       <c r="E513" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F513" t="s">
         <v>871</v>
@@ -13330,7 +13331,7 @@
         <v>393</v>
       </c>
       <c r="E514" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F514" t="s">
         <v>871</v>
@@ -13350,7 +13351,7 @@
         <v>393</v>
       </c>
       <c r="E515" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F515" t="s">
         <v>871</v>
@@ -13370,7 +13371,7 @@
         <v>393</v>
       </c>
       <c r="E516" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F516" t="s">
         <v>871</v>
@@ -13390,7 +13391,7 @@
         <v>393</v>
       </c>
       <c r="E517" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F517" t="s">
         <v>871</v>
@@ -13410,7 +13411,7 @@
         <v>393</v>
       </c>
       <c r="E518" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F518" t="s">
         <v>871</v>
@@ -13430,7 +13431,7 @@
         <v>393</v>
       </c>
       <c r="E519" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F519" t="s">
         <v>871</v>
@@ -13450,7 +13451,7 @@
         <v>393</v>
       </c>
       <c r="E520" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F520" t="s">
         <v>871</v>
@@ -13470,7 +13471,7 @@
         <v>393</v>
       </c>
       <c r="E521" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F521" t="s">
         <v>871</v>
@@ -13490,7 +13491,7 @@
         <v>393</v>
       </c>
       <c r="E522" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F522" t="s">
         <v>871</v>
@@ -13510,7 +13511,7 @@
         <v>393</v>
       </c>
       <c r="E523" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F523" t="s">
         <v>871</v>
@@ -13530,7 +13531,7 @@
         <v>393</v>
       </c>
       <c r="E524" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>871</v>
@@ -13550,7 +13551,7 @@
         <v>393</v>
       </c>
       <c r="E525" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F525" t="s">
         <v>871</v>
@@ -13570,7 +13571,7 @@
         <v>393</v>
       </c>
       <c r="E526" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>871</v>
@@ -13590,7 +13591,7 @@
         <v>393</v>
       </c>
       <c r="E527" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F527" t="s">
         <v>871</v>
@@ -13610,7 +13611,7 @@
         <v>393</v>
       </c>
       <c r="E528" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F528" t="s">
         <v>871</v>
@@ -13630,7 +13631,7 @@
         <v>393</v>
       </c>
       <c r="E529" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F529" t="s">
         <v>871</v>
@@ -13650,7 +13651,7 @@
         <v>393</v>
       </c>
       <c r="E530" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F530" t="s">
         <v>871</v>
@@ -13670,7 +13671,7 @@
         <v>393</v>
       </c>
       <c r="E531" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F531" t="s">
         <v>871</v>
@@ -13690,7 +13691,7 @@
         <v>393</v>
       </c>
       <c r="E532" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F532" t="s">
         <v>871</v>
@@ -13710,7 +13711,7 @@
         <v>393</v>
       </c>
       <c r="E533" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F533" t="s">
         <v>871</v>
@@ -13730,7 +13731,7 @@
         <v>393</v>
       </c>
       <c r="E534" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F534" t="s">
         <v>871</v>
@@ -13750,7 +13751,7 @@
         <v>393</v>
       </c>
       <c r="E535" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F535" t="s">
         <v>871</v>
@@ -13770,7 +13771,7 @@
         <v>393</v>
       </c>
       <c r="E536" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F536" t="s">
         <v>871</v>
@@ -13790,7 +13791,7 @@
         <v>393</v>
       </c>
       <c r="E537" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F537" t="s">
         <v>871</v>
@@ -13810,7 +13811,7 @@
         <v>393</v>
       </c>
       <c r="E538" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F538" t="s">
         <v>871</v>
@@ -13830,7 +13831,7 @@
         <v>393</v>
       </c>
       <c r="E539" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>871</v>
@@ -13850,7 +13851,7 @@
         <v>393</v>
       </c>
       <c r="E540" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F540" t="s">
         <v>871</v>
@@ -13870,7 +13871,7 @@
         <v>393</v>
       </c>
       <c r="E541" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F541" t="s">
         <v>871</v>
@@ -13890,7 +13891,7 @@
         <v>393</v>
       </c>
       <c r="E542" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F542" t="s">
         <v>871</v>
@@ -13910,7 +13911,7 @@
         <v>393</v>
       </c>
       <c r="E543" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F543" t="s">
         <v>871</v>
@@ -13930,7 +13931,7 @@
         <v>393</v>
       </c>
       <c r="E544" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F544" t="s">
         <v>871</v>
@@ -13950,7 +13951,7 @@
         <v>393</v>
       </c>
       <c r="E545" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F545" t="s">
         <v>871</v>
@@ -13970,7 +13971,7 @@
         <v>393</v>
       </c>
       <c r="E546" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F546" t="s">
         <v>871</v>
@@ -13990,7 +13991,7 @@
         <v>393</v>
       </c>
       <c r="E547" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F547" t="s">
         <v>871</v>
@@ -14010,7 +14011,7 @@
         <v>393</v>
       </c>
       <c r="E548" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F548" t="s">
         <v>871</v>
@@ -14030,7 +14031,7 @@
         <v>393</v>
       </c>
       <c r="E549" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F549" t="s">
         <v>871</v>
@@ -14050,7 +14051,7 @@
         <v>393</v>
       </c>
       <c r="E550" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F550" t="s">
         <v>871</v>
@@ -14070,7 +14071,7 @@
         <v>393</v>
       </c>
       <c r="E551" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F551" t="s">
         <v>871</v>
@@ -14090,7 +14091,7 @@
         <v>393</v>
       </c>
       <c r="E552" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F552" t="s">
         <v>871</v>
@@ -14110,7 +14111,7 @@
         <v>393</v>
       </c>
       <c r="E553" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F553" t="s">
         <v>871</v>
@@ -14130,7 +14131,7 @@
         <v>393</v>
       </c>
       <c r="E554" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F554" t="s">
         <v>871</v>
@@ -14150,7 +14151,7 @@
         <v>393</v>
       </c>
       <c r="E555" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F555" t="s">
         <v>871</v>
@@ -14170,7 +14171,7 @@
         <v>393</v>
       </c>
       <c r="E556" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F556" t="s">
         <v>871</v>
@@ -14190,7 +14191,7 @@
         <v>393</v>
       </c>
       <c r="E557" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F557" t="s">
         <v>871</v>
@@ -14210,7 +14211,7 @@
         <v>393</v>
       </c>
       <c r="E558" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F558" t="s">
         <v>871</v>
@@ -14230,7 +14231,7 @@
         <v>393</v>
       </c>
       <c r="E559" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F559" t="s">
         <v>871</v>
@@ -14250,7 +14251,7 @@
         <v>393</v>
       </c>
       <c r="E560" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F560" t="s">
         <v>871</v>
@@ -14270,7 +14271,7 @@
         <v>393</v>
       </c>
       <c r="E561" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F561" t="s">
         <v>871</v>
@@ -14290,7 +14291,7 @@
         <v>393</v>
       </c>
       <c r="E562" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F562" t="s">
         <v>871</v>
@@ -14310,7 +14311,7 @@
         <v>393</v>
       </c>
       <c r="E563" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F563" t="s">
         <v>871</v>
@@ -14330,7 +14331,7 @@
         <v>393</v>
       </c>
       <c r="E564" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F564" t="s">
         <v>871</v>
@@ -14350,7 +14351,7 @@
         <v>393</v>
       </c>
       <c r="E565" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F565" t="s">
         <v>871</v>
@@ -14370,7 +14371,7 @@
         <v>393</v>
       </c>
       <c r="E566" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F566" t="s">
         <v>871</v>
@@ -14390,7 +14391,7 @@
         <v>393</v>
       </c>
       <c r="E567" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F567" t="s">
         <v>871</v>
@@ -14410,7 +14411,7 @@
         <v>393</v>
       </c>
       <c r="E568" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F568" t="s">
         <v>871</v>
@@ -14430,7 +14431,7 @@
         <v>393</v>
       </c>
       <c r="E569" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F569" t="s">
         <v>871</v>
@@ -14450,7 +14451,7 @@
         <v>393</v>
       </c>
       <c r="E570" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F570" t="s">
         <v>871</v>
@@ -14470,7 +14471,7 @@
         <v>393</v>
       </c>
       <c r="E571" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F571" t="s">
         <v>871</v>
@@ -14490,7 +14491,7 @@
         <v>393</v>
       </c>
       <c r="E572" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F572" t="s">
         <v>871</v>
@@ -14510,7 +14511,7 @@
         <v>393</v>
       </c>
       <c r="E573" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F573" t="s">
         <v>871</v>
@@ -14530,7 +14531,7 @@
         <v>393</v>
       </c>
       <c r="E574" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F574" t="s">
         <v>871</v>
@@ -14550,7 +14551,7 @@
         <v>393</v>
       </c>
       <c r="E575" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F575" t="s">
         <v>871</v>
@@ -14570,7 +14571,7 @@
         <v>393</v>
       </c>
       <c r="E576" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F576" t="s">
         <v>871</v>
@@ -14590,7 +14591,7 @@
         <v>393</v>
       </c>
       <c r="E577" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F577" t="s">
         <v>871</v>
@@ -14610,7 +14611,7 @@
         <v>393</v>
       </c>
       <c r="E578" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F578" t="s">
         <v>871</v>
@@ -14630,7 +14631,7 @@
         <v>393</v>
       </c>
       <c r="E579" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F579" t="s">
         <v>871</v>
@@ -14650,7 +14651,7 @@
         <v>393</v>
       </c>
       <c r="E580" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F580" t="s">
         <v>871</v>
@@ -14670,7 +14671,7 @@
         <v>393</v>
       </c>
       <c r="E581" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F581" t="s">
         <v>871</v>
@@ -14690,7 +14691,7 @@
         <v>393</v>
       </c>
       <c r="E582" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F582" t="s">
         <v>871</v>
@@ -14710,7 +14711,7 @@
         <v>393</v>
       </c>
       <c r="E583" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F583" t="s">
         <v>871</v>
@@ -14730,7 +14731,7 @@
         <v>393</v>
       </c>
       <c r="E584" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F584" t="s">
         <v>871</v>
@@ -14750,7 +14751,7 @@
         <v>393</v>
       </c>
       <c r="E585" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F585" t="s">
         <v>871</v>
@@ -14770,7 +14771,7 @@
         <v>393</v>
       </c>
       <c r="E586" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F586" t="s">
         <v>871</v>
@@ -14790,7 +14791,7 @@
         <v>393</v>
       </c>
       <c r="E587" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F587" t="s">
         <v>871</v>
@@ -14810,7 +14811,7 @@
         <v>393</v>
       </c>
       <c r="E588" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F588" t="s">
         <v>871</v>
@@ -14830,7 +14831,7 @@
         <v>393</v>
       </c>
       <c r="E589" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F589" t="s">
         <v>871</v>
@@ -14850,7 +14851,7 @@
         <v>393</v>
       </c>
       <c r="E590" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F590" t="s">
         <v>871</v>
@@ -14870,7 +14871,7 @@
         <v>393</v>
       </c>
       <c r="E591" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F591" t="s">
         <v>871</v>
@@ -14890,7 +14891,7 @@
         <v>393</v>
       </c>
       <c r="E592" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F592" t="s">
         <v>871</v>
@@ -14910,7 +14911,7 @@
         <v>393</v>
       </c>
       <c r="E593" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F593" t="s">
         <v>871</v>
@@ -14930,7 +14931,7 @@
         <v>393</v>
       </c>
       <c r="E594" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F594" t="s">
         <v>871</v>
@@ -14950,7 +14951,7 @@
         <v>393</v>
       </c>
       <c r="E595" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F595" t="s">
         <v>871</v>
@@ -14970,7 +14971,7 @@
         <v>393</v>
       </c>
       <c r="E596" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F596" t="s">
         <v>871</v>
@@ -14990,7 +14991,7 @@
         <v>393</v>
       </c>
       <c r="E597" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F597" t="s">
         <v>871</v>
@@ -15010,7 +15011,7 @@
         <v>393</v>
       </c>
       <c r="E598" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F598" t="s">
         <v>871</v>
@@ -15030,7 +15031,7 @@
         <v>393</v>
       </c>
       <c r="E599" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F599" t="s">
         <v>871</v>
@@ -15050,7 +15051,7 @@
         <v>393</v>
       </c>
       <c r="E600" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F600" t="s">
         <v>871</v>
@@ -15070,7 +15071,7 @@
         <v>393</v>
       </c>
       <c r="E601" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F601" t="s">
         <v>871</v>
@@ -15090,7 +15091,7 @@
         <v>393</v>
       </c>
       <c r="E602" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F602" t="s">
         <v>871</v>
@@ -15110,7 +15111,7 @@
         <v>393</v>
       </c>
       <c r="E603" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F603" t="s">
         <v>871</v>
@@ -15130,7 +15131,7 @@
         <v>393</v>
       </c>
       <c r="E604" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F604" t="s">
         <v>871</v>
@@ -15150,7 +15151,7 @@
         <v>393</v>
       </c>
       <c r="E605" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F605" t="s">
         <v>871</v>
@@ -15170,7 +15171,7 @@
         <v>393</v>
       </c>
       <c r="E606" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F606" t="s">
         <v>871</v>
@@ -15190,7 +15191,7 @@
         <v>393</v>
       </c>
       <c r="E607" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F607" t="s">
         <v>871</v>
@@ -15210,7 +15211,7 @@
         <v>393</v>
       </c>
       <c r="E608" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F608" t="s">
         <v>871</v>
@@ -15230,7 +15231,7 @@
         <v>393</v>
       </c>
       <c r="E609" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F609" t="s">
         <v>871</v>
@@ -15250,7 +15251,7 @@
         <v>393</v>
       </c>
       <c r="E610" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F610" t="s">
         <v>871</v>
@@ -15270,7 +15271,7 @@
         <v>393</v>
       </c>
       <c r="E611" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F611" t="s">
         <v>871</v>
@@ -15290,7 +15291,7 @@
         <v>393</v>
       </c>
       <c r="E612" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F612" t="s">
         <v>871</v>
@@ -15310,7 +15311,7 @@
         <v>393</v>
       </c>
       <c r="E613" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F613" t="s">
         <v>871</v>
@@ -15330,7 +15331,7 @@
         <v>393</v>
       </c>
       <c r="E614" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F614" t="s">
         <v>871</v>
@@ -15350,7 +15351,7 @@
         <v>393</v>
       </c>
       <c r="E615" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F615" t="s">
         <v>871</v>
@@ -15370,7 +15371,7 @@
         <v>393</v>
       </c>
       <c r="E616" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F616" t="s">
         <v>871</v>
@@ -15390,7 +15391,7 @@
         <v>393</v>
       </c>
       <c r="E617" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F617" t="s">
         <v>871</v>
@@ -15410,7 +15411,7 @@
         <v>393</v>
       </c>
       <c r="E618" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F618" t="s">
         <v>871</v>
@@ -15430,7 +15431,7 @@
         <v>393</v>
       </c>
       <c r="E619" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F619" t="s">
         <v>871</v>
@@ -15450,7 +15451,7 @@
         <v>393</v>
       </c>
       <c r="E620" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F620" t="s">
         <v>871</v>
@@ -15470,7 +15471,7 @@
         <v>393</v>
       </c>
       <c r="E621" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F621" t="s">
         <v>871</v>
@@ -15490,7 +15491,7 @@
         <v>393</v>
       </c>
       <c r="E622" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F622" t="s">
         <v>871</v>
@@ -15510,7 +15511,7 @@
         <v>393</v>
       </c>
       <c r="E623" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F623" t="s">
         <v>871</v>
@@ -15530,7 +15531,7 @@
         <v>393</v>
       </c>
       <c r="E624" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F624" t="s">
         <v>871</v>
@@ -15550,7 +15551,7 @@
         <v>393</v>
       </c>
       <c r="E625" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F625" t="s">
         <v>871</v>
@@ -15570,7 +15571,7 @@
         <v>393</v>
       </c>
       <c r="E626" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F626" t="s">
         <v>871</v>
@@ -15590,7 +15591,7 @@
         <v>393</v>
       </c>
       <c r="E627" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F627" t="s">
         <v>871</v>
@@ -15610,7 +15611,7 @@
         <v>393</v>
       </c>
       <c r="E628" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F628" t="s">
         <v>871</v>
@@ -15630,7 +15631,7 @@
         <v>393</v>
       </c>
       <c r="E629" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F629" t="s">
         <v>871</v>
@@ -15650,7 +15651,7 @@
         <v>393</v>
       </c>
       <c r="E630" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F630" t="s">
         <v>871</v>
@@ -15670,7 +15671,7 @@
         <v>393</v>
       </c>
       <c r="E631" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F631" t="s">
         <v>871</v>
@@ -15690,7 +15691,7 @@
         <v>393</v>
       </c>
       <c r="E632" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F632" t="s">
         <v>871</v>
@@ -15710,7 +15711,7 @@
         <v>393</v>
       </c>
       <c r="E633" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F633" t="s">
         <v>871</v>
@@ -15730,7 +15731,7 @@
         <v>393</v>
       </c>
       <c r="E634" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F634" t="s">
         <v>871</v>
@@ -15750,7 +15751,7 @@
         <v>393</v>
       </c>
       <c r="E635" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F635" t="s">
         <v>871</v>
@@ -15770,7 +15771,7 @@
         <v>393</v>
       </c>
       <c r="E636" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F636" t="s">
         <v>871</v>
@@ -15790,7 +15791,7 @@
         <v>393</v>
       </c>
       <c r="E637" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F637" t="s">
         <v>871</v>
@@ -15810,7 +15811,7 @@
         <v>393</v>
       </c>
       <c r="E638" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F638" t="s">
         <v>871</v>
@@ -15830,7 +15831,7 @@
         <v>393</v>
       </c>
       <c r="E639" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F639" t="s">
         <v>871</v>
@@ -15850,7 +15851,7 @@
         <v>393</v>
       </c>
       <c r="E640" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F640" t="s">
         <v>871</v>
@@ -15870,7 +15871,7 @@
         <v>393</v>
       </c>
       <c r="E641" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F641" t="s">
         <v>871</v>
@@ -15890,7 +15891,7 @@
         <v>393</v>
       </c>
       <c r="E642" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F642" t="s">
         <v>871</v>
@@ -15910,7 +15911,7 @@
         <v>393</v>
       </c>
       <c r="E643" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F643" t="s">
         <v>871</v>
@@ -15930,7 +15931,7 @@
         <v>393</v>
       </c>
       <c r="E644" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F644" t="s">
         <v>871</v>
@@ -15950,7 +15951,7 @@
         <v>393</v>
       </c>
       <c r="E645" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F645" t="s">
         <v>871</v>
@@ -15970,7 +15971,7 @@
         <v>393</v>
       </c>
       <c r="E646" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F646" t="s">
         <v>871</v>
@@ -15990,7 +15991,7 @@
         <v>393</v>
       </c>
       <c r="E647" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F647" t="s">
         <v>871</v>
@@ -16010,7 +16011,7 @@
         <v>393</v>
       </c>
       <c r="E648" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F648" t="s">
         <v>871</v>
@@ -16030,7 +16031,7 @@
         <v>393</v>
       </c>
       <c r="E649" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F649" t="s">
         <v>871</v>
@@ -16050,7 +16051,7 @@
         <v>393</v>
       </c>
       <c r="E650" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F650" t="s">
         <v>871</v>
@@ -16070,7 +16071,7 @@
         <v>393</v>
       </c>
       <c r="E651" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F651" t="s">
         <v>871</v>
@@ -16090,7 +16091,7 @@
         <v>393</v>
       </c>
       <c r="E652" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F652" t="s">
         <v>871</v>
@@ -16110,7 +16111,7 @@
         <v>393</v>
       </c>
       <c r="E653" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F653" t="s">
         <v>871</v>
@@ -16130,7 +16131,7 @@
         <v>393</v>
       </c>
       <c r="E654" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F654" t="s">
         <v>871</v>
@@ -16150,7 +16151,7 @@
         <v>393</v>
       </c>
       <c r="E655" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F655" t="s">
         <v>871</v>
@@ -16170,7 +16171,7 @@
         <v>393</v>
       </c>
       <c r="E656" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F656" t="s">
         <v>871</v>
@@ -16190,7 +16191,7 @@
         <v>393</v>
       </c>
       <c r="E657" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F657" t="s">
         <v>871</v>
@@ -16210,7 +16211,7 @@
         <v>393</v>
       </c>
       <c r="E658" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F658" t="s">
         <v>871</v>
@@ -16230,7 +16231,7 @@
         <v>393</v>
       </c>
       <c r="E659" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F659" t="s">
         <v>871</v>
@@ -16250,7 +16251,7 @@
         <v>393</v>
       </c>
       <c r="E660" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F660" t="s">
         <v>871</v>
@@ -16270,7 +16271,7 @@
         <v>393</v>
       </c>
       <c r="E661" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F661" t="s">
         <v>871</v>
@@ -16290,7 +16291,7 @@
         <v>393</v>
       </c>
       <c r="E662" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F662" t="s">
         <v>871</v>
@@ -16310,7 +16311,7 @@
         <v>393</v>
       </c>
       <c r="E663" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F663" t="s">
         <v>871</v>
@@ -16330,7 +16331,7 @@
         <v>393</v>
       </c>
       <c r="E664" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F664" t="s">
         <v>871</v>
@@ -16350,7 +16351,7 @@
         <v>393</v>
       </c>
       <c r="E665" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F665" t="s">
         <v>871</v>
@@ -16370,7 +16371,7 @@
         <v>393</v>
       </c>
       <c r="E666" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F666" t="s">
         <v>871</v>
@@ -16390,7 +16391,7 @@
         <v>393</v>
       </c>
       <c r="E667" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F667" t="s">
         <v>871</v>
@@ -16410,7 +16411,7 @@
         <v>393</v>
       </c>
       <c r="E668" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F668" t="s">
         <v>871</v>
@@ -16430,7 +16431,7 @@
         <v>393</v>
       </c>
       <c r="E669" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F669" t="s">
         <v>871</v>
@@ -16450,7 +16451,7 @@
         <v>393</v>
       </c>
       <c r="E670" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F670" t="s">
         <v>871</v>
@@ -16470,7 +16471,7 @@
         <v>393</v>
       </c>
       <c r="E671" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F671" t="s">
         <v>871</v>
@@ -16490,7 +16491,7 @@
         <v>393</v>
       </c>
       <c r="E672" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F672" t="s">
         <v>871</v>
@@ -16510,7 +16511,7 @@
         <v>393</v>
       </c>
       <c r="E673" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F673" t="s">
         <v>871</v>
@@ -16530,7 +16531,7 @@
         <v>393</v>
       </c>
       <c r="E674" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F674" t="s">
         <v>871</v>
@@ -16550,7 +16551,7 @@
         <v>393</v>
       </c>
       <c r="E675" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F675" t="s">
         <v>871</v>
@@ -16570,7 +16571,7 @@
         <v>393</v>
       </c>
       <c r="E676" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F676" t="s">
         <v>871</v>
@@ -16590,7 +16591,7 @@
         <v>393</v>
       </c>
       <c r="E677" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F677" t="s">
         <v>871</v>
@@ -16610,7 +16611,7 @@
         <v>393</v>
       </c>
       <c r="E678" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F678" t="s">
         <v>871</v>
@@ -16630,7 +16631,7 @@
         <v>393</v>
       </c>
       <c r="E679" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F679" t="s">
         <v>871</v>
@@ -16650,7 +16651,7 @@
         <v>393</v>
       </c>
       <c r="E680" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F680" t="s">
         <v>871</v>
@@ -16670,7 +16671,7 @@
         <v>393</v>
       </c>
       <c r="E681" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F681" t="s">
         <v>871</v>
@@ -16690,7 +16691,7 @@
         <v>393</v>
       </c>
       <c r="E682" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F682" t="s">
         <v>871</v>
@@ -16710,7 +16711,7 @@
         <v>393</v>
       </c>
       <c r="E683" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F683" t="s">
         <v>871</v>
@@ -16730,7 +16731,7 @@
         <v>393</v>
       </c>
       <c r="E684" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F684" t="s">
         <v>871</v>
@@ -16750,7 +16751,7 @@
         <v>393</v>
       </c>
       <c r="E685" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F685" t="s">
         <v>871</v>
@@ -16770,7 +16771,7 @@
         <v>393</v>
       </c>
       <c r="E686" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F686" t="s">
         <v>871</v>
@@ -16790,7 +16791,7 @@
         <v>393</v>
       </c>
       <c r="E687" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F687" t="s">
         <v>871</v>
@@ -16810,7 +16811,7 @@
         <v>393</v>
       </c>
       <c r="E688" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F688" t="s">
         <v>871</v>
@@ -16830,7 +16831,7 @@
         <v>393</v>
       </c>
       <c r="E689" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F689" t="s">
         <v>871</v>
@@ -16850,7 +16851,7 @@
         <v>393</v>
       </c>
       <c r="E690" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F690" t="s">
         <v>871</v>
@@ -16870,7 +16871,7 @@
         <v>393</v>
       </c>
       <c r="E691" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F691" t="s">
         <v>871</v>
@@ -16890,7 +16891,7 @@
         <v>393</v>
       </c>
       <c r="E692" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F692" t="s">
         <v>871</v>
@@ -16910,7 +16911,7 @@
         <v>393</v>
       </c>
       <c r="E693" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F693" t="s">
         <v>871</v>
@@ -16930,7 +16931,7 @@
         <v>393</v>
       </c>
       <c r="E694" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F694" t="s">
         <v>871</v>
@@ -16950,7 +16951,7 @@
         <v>393</v>
       </c>
       <c r="E695" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F695" t="s">
         <v>871</v>
@@ -16970,7 +16971,7 @@
         <v>393</v>
       </c>
       <c r="E696" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F696" t="s">
         <v>871</v>
@@ -16990,7 +16991,7 @@
         <v>393</v>
       </c>
       <c r="E697" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F697" t="s">
         <v>871</v>
@@ -17010,7 +17011,7 @@
         <v>393</v>
       </c>
       <c r="E698" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F698" t="s">
         <v>871</v>
@@ -17030,7 +17031,7 @@
         <v>393</v>
       </c>
       <c r="E699" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F699" t="s">
         <v>871</v>
@@ -17050,7 +17051,7 @@
         <v>393</v>
       </c>
       <c r="E700" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F700" t="s">
         <v>871</v>
@@ -17070,7 +17071,7 @@
         <v>393</v>
       </c>
       <c r="E701" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F701" t="s">
         <v>871</v>
@@ -17090,7 +17091,7 @@
         <v>393</v>
       </c>
       <c r="E702" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F702" t="s">
         <v>871</v>
@@ -17110,7 +17111,7 @@
         <v>393</v>
       </c>
       <c r="E703" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F703" t="s">
         <v>871</v>
@@ -17130,7 +17131,7 @@
         <v>393</v>
       </c>
       <c r="E704" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F704" t="s">
         <v>871</v>
@@ -17150,7 +17151,7 @@
         <v>393</v>
       </c>
       <c r="E705" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F705" t="s">
         <v>871</v>
@@ -17170,7 +17171,7 @@
         <v>393</v>
       </c>
       <c r="E706" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F706" t="s">
         <v>871</v>
@@ -17190,7 +17191,7 @@
         <v>393</v>
       </c>
       <c r="E707" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F707" t="s">
         <v>871</v>
@@ -17210,7 +17211,7 @@
         <v>393</v>
       </c>
       <c r="E708" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F708" t="s">
         <v>871</v>
@@ -17230,7 +17231,7 @@
         <v>393</v>
       </c>
       <c r="E709" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F709" t="s">
         <v>871</v>
@@ -17250,7 +17251,7 @@
         <v>393</v>
       </c>
       <c r="E710" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F710" t="s">
         <v>871</v>
@@ -17270,7 +17271,7 @@
         <v>393</v>
       </c>
       <c r="E711" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F711" t="s">
         <v>871</v>
@@ -17290,7 +17291,7 @@
         <v>393</v>
       </c>
       <c r="E712" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F712" t="s">
         <v>871</v>
@@ -17310,7 +17311,7 @@
         <v>393</v>
       </c>
       <c r="E713" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F713" t="s">
         <v>871</v>
@@ -17330,7 +17331,7 @@
         <v>393</v>
       </c>
       <c r="E714" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F714" t="s">
         <v>871</v>
@@ -17350,7 +17351,7 @@
         <v>393</v>
       </c>
       <c r="E715" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F715" t="s">
         <v>871</v>
@@ -17370,7 +17371,7 @@
         <v>393</v>
       </c>
       <c r="E716" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F716" t="s">
         <v>871</v>
@@ -17390,7 +17391,7 @@
         <v>393</v>
       </c>
       <c r="E717" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F717" t="s">
         <v>871</v>
@@ -17410,7 +17411,7 @@
         <v>393</v>
       </c>
       <c r="E718" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F718" t="s">
         <v>871</v>
@@ -17430,7 +17431,7 @@
         <v>393</v>
       </c>
       <c r="E719" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F719" t="s">
         <v>871</v>
@@ -17450,7 +17451,7 @@
         <v>393</v>
       </c>
       <c r="E720" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F720" t="s">
         <v>871</v>
@@ -17470,7 +17471,7 @@
         <v>393</v>
       </c>
       <c r="E721" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F721" t="s">
         <v>871</v>
@@ -17490,7 +17491,7 @@
         <v>393</v>
       </c>
       <c r="E722" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F722" t="s">
         <v>871</v>
@@ -17510,7 +17511,7 @@
         <v>393</v>
       </c>
       <c r="E723" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F723" t="s">
         <v>871</v>
@@ -17530,7 +17531,7 @@
         <v>393</v>
       </c>
       <c r="E724" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F724" t="s">
         <v>871</v>
@@ -17550,7 +17551,7 @@
         <v>393</v>
       </c>
       <c r="E725" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F725" t="s">
         <v>871</v>
@@ -17570,7 +17571,7 @@
         <v>393</v>
       </c>
       <c r="E726" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F726" t="s">
         <v>871</v>
@@ -17590,7 +17591,7 @@
         <v>393</v>
       </c>
       <c r="E727" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F727" t="s">
         <v>871</v>
@@ -17610,7 +17611,7 @@
         <v>393</v>
       </c>
       <c r="E728" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F728" t="s">
         <v>871</v>
@@ -17630,7 +17631,7 @@
         <v>393</v>
       </c>
       <c r="E729" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F729" t="s">
         <v>871</v>
@@ -17650,7 +17651,7 @@
         <v>393</v>
       </c>
       <c r="E730" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F730" t="s">
         <v>871</v>
@@ -17670,7 +17671,7 @@
         <v>393</v>
       </c>
       <c r="E731" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F731" t="s">
         <v>871</v>
@@ -17690,7 +17691,7 @@
         <v>393</v>
       </c>
       <c r="E732" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F732" t="s">
         <v>871</v>
@@ -17710,7 +17711,7 @@
         <v>393</v>
       </c>
       <c r="E733" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F733" t="s">
         <v>871</v>
@@ -17730,7 +17731,7 @@
         <v>393</v>
       </c>
       <c r="E734" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F734" t="s">
         <v>871</v>
@@ -17750,7 +17751,7 @@
         <v>393</v>
       </c>
       <c r="E735" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F735" t="s">
         <v>871</v>
@@ -17770,7 +17771,7 @@
         <v>393</v>
       </c>
       <c r="E736" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F736" t="s">
         <v>871</v>
@@ -17790,7 +17791,7 @@
         <v>393</v>
       </c>
       <c r="E737" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F737" t="s">
         <v>871</v>
@@ -17810,7 +17811,7 @@
         <v>393</v>
       </c>
       <c r="E738" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F738" t="s">
         <v>871</v>
@@ -17830,7 +17831,7 @@
         <v>393</v>
       </c>
       <c r="E739" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F739" t="s">
         <v>871</v>
@@ -17850,7 +17851,7 @@
         <v>393</v>
       </c>
       <c r="E740" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F740" t="s">
         <v>871</v>
@@ -17870,7 +17871,7 @@
         <v>393</v>
       </c>
       <c r="E741" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F741" t="s">
         <v>871</v>
@@ -17890,7 +17891,7 @@
         <v>393</v>
       </c>
       <c r="E742" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F742" t="s">
         <v>871</v>
@@ -17910,7 +17911,7 @@
         <v>393</v>
       </c>
       <c r="E743" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F743" t="s">
         <v>871</v>
@@ -17930,7 +17931,7 @@
         <v>393</v>
       </c>
       <c r="E744" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F744" t="s">
         <v>871</v>
@@ -17950,7 +17951,7 @@
         <v>393</v>
       </c>
       <c r="E745" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F745" t="s">
         <v>871</v>
@@ -17970,7 +17971,7 @@
         <v>393</v>
       </c>
       <c r="E746" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F746" t="s">
         <v>871</v>
@@ -17990,7 +17991,7 @@
         <v>393</v>
       </c>
       <c r="E747" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F747" t="s">
         <v>871</v>
@@ -18010,7 +18011,7 @@
         <v>393</v>
       </c>
       <c r="E748" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F748" t="s">
         <v>871</v>
@@ -18030,7 +18031,7 @@
         <v>393</v>
       </c>
       <c r="E749" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F749" t="s">
         <v>871</v>
@@ -18050,7 +18051,7 @@
         <v>393</v>
       </c>
       <c r="E750" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F750" t="s">
         <v>871</v>
@@ -18070,7 +18071,7 @@
         <v>393</v>
       </c>
       <c r="E751" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F751" t="s">
         <v>871</v>
@@ -18090,7 +18091,7 @@
         <v>393</v>
       </c>
       <c r="E752" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F752" t="s">
         <v>871</v>
@@ -18110,7 +18111,7 @@
         <v>393</v>
       </c>
       <c r="E753" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F753" t="s">
         <v>871</v>
@@ -18130,7 +18131,7 @@
         <v>393</v>
       </c>
       <c r="E754" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F754" t="s">
         <v>871</v>
@@ -18150,7 +18151,7 @@
         <v>393</v>
       </c>
       <c r="E755" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F755" t="s">
         <v>871</v>
@@ -18170,7 +18171,7 @@
         <v>393</v>
       </c>
       <c r="E756" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F756" t="s">
         <v>871</v>
@@ -18190,7 +18191,7 @@
         <v>393</v>
       </c>
       <c r="E757" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F757" t="s">
         <v>871</v>
@@ -18210,7 +18211,7 @@
         <v>393</v>
       </c>
       <c r="E758" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F758" t="s">
         <v>871</v>
@@ -18230,7 +18231,7 @@
         <v>393</v>
       </c>
       <c r="E759" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F759" t="s">
         <v>871</v>
@@ -18250,7 +18251,7 @@
         <v>393</v>
       </c>
       <c r="E760" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F760" t="s">
         <v>871</v>
@@ -18270,7 +18271,7 @@
         <v>393</v>
       </c>
       <c r="E761" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F761" t="s">
         <v>871</v>
@@ -18290,7 +18291,7 @@
         <v>393</v>
       </c>
       <c r="E762" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F762" t="s">
         <v>871</v>
@@ -18310,7 +18311,7 @@
         <v>393</v>
       </c>
       <c r="E763" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F763" t="s">
         <v>871</v>
@@ -18330,7 +18331,7 @@
         <v>393</v>
       </c>
       <c r="E764" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F764" t="s">
         <v>871</v>
@@ -18350,7 +18351,7 @@
         <v>393</v>
       </c>
       <c r="E765" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F765" t="s">
         <v>871</v>
@@ -18370,7 +18371,7 @@
         <v>393</v>
       </c>
       <c r="E766" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F766" t="s">
         <v>871</v>
@@ -18390,7 +18391,7 @@
         <v>393</v>
       </c>
       <c r="E767" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F767" t="s">
         <v>871</v>
@@ -18410,7 +18411,7 @@
         <v>393</v>
       </c>
       <c r="E768" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F768" t="s">
         <v>871</v>
@@ -18430,7 +18431,7 @@
         <v>393</v>
       </c>
       <c r="E769" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F769" t="s">
         <v>871</v>
@@ -18450,7 +18451,7 @@
         <v>393</v>
       </c>
       <c r="E770" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F770" t="s">
         <v>871</v>
@@ -18470,7 +18471,7 @@
         <v>393</v>
       </c>
       <c r="E771" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F771" t="s">
         <v>871</v>
@@ -18490,7 +18491,7 @@
         <v>393</v>
       </c>
       <c r="E772" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F772" t="s">
         <v>871</v>
@@ -18510,7 +18511,7 @@
         <v>393</v>
       </c>
       <c r="E773" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F773" t="s">
         <v>871</v>
@@ -18530,7 +18531,7 @@
         <v>393</v>
       </c>
       <c r="E774" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F774" t="s">
         <v>871</v>
@@ -18550,7 +18551,7 @@
         <v>393</v>
       </c>
       <c r="E775" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F775" t="s">
         <v>871</v>
@@ -18570,7 +18571,7 @@
         <v>393</v>
       </c>
       <c r="E776" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F776" t="s">
         <v>871</v>
@@ -18590,7 +18591,7 @@
         <v>393</v>
       </c>
       <c r="E777" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F777" t="s">
         <v>871</v>
@@ -18610,7 +18611,7 @@
         <v>393</v>
       </c>
       <c r="E778" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F778" t="s">
         <v>871</v>
@@ -18630,7 +18631,7 @@
         <v>393</v>
       </c>
       <c r="E779" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F779" t="s">
         <v>871</v>
@@ -18650,7 +18651,7 @@
         <v>393</v>
       </c>
       <c r="E780" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F780" t="s">
         <v>871</v>
@@ -18670,7 +18671,7 @@
         <v>393</v>
       </c>
       <c r="E781" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F781" t="s">
         <v>871</v>
@@ -18690,7 +18691,7 @@
         <v>393</v>
       </c>
       <c r="E782" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F782" t="s">
         <v>871</v>
@@ -18710,7 +18711,7 @@
         <v>393</v>
       </c>
       <c r="E783" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F783" t="s">
         <v>871</v>
@@ -18730,7 +18731,7 @@
         <v>393</v>
       </c>
       <c r="E784" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F784" t="s">
         <v>871</v>
@@ -18750,7 +18751,7 @@
         <v>393</v>
       </c>
       <c r="E785" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F785" t="s">
         <v>871</v>
@@ -18770,7 +18771,7 @@
         <v>393</v>
       </c>
       <c r="E786" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F786" t="s">
         <v>871</v>
@@ -18790,7 +18791,7 @@
         <v>393</v>
       </c>
       <c r="E787" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F787" t="s">
         <v>871</v>
@@ -18810,7 +18811,7 @@
         <v>393</v>
       </c>
       <c r="E788" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F788" t="s">
         <v>871</v>
@@ -18830,7 +18831,7 @@
         <v>393</v>
       </c>
       <c r="E789" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F789" t="s">
         <v>871</v>
@@ -18850,7 +18851,7 @@
         <v>393</v>
       </c>
       <c r="E790" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F790" t="s">
         <v>871</v>
@@ -18870,7 +18871,7 @@
         <v>393</v>
       </c>
       <c r="E791" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F791" t="s">
         <v>871</v>
@@ -18890,7 +18891,7 @@
         <v>393</v>
       </c>
       <c r="E792" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F792" t="s">
         <v>871</v>
@@ -18910,7 +18911,7 @@
         <v>393</v>
       </c>
       <c r="E793" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F793" t="s">
         <v>871</v>
@@ -18930,7 +18931,7 @@
         <v>393</v>
       </c>
       <c r="E794" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F794" t="s">
         <v>871</v>
@@ -18950,7 +18951,7 @@
         <v>393</v>
       </c>
       <c r="E795" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F795" t="s">
         <v>871</v>
@@ -18970,7 +18971,7 @@
         <v>393</v>
       </c>
       <c r="E796" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F796" t="s">
         <v>871</v>
@@ -18990,7 +18991,7 @@
         <v>393</v>
       </c>
       <c r="E797" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F797" t="s">
         <v>871</v>
@@ -19010,7 +19011,7 @@
         <v>393</v>
       </c>
       <c r="E798" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F798" t="s">
         <v>871</v>
@@ -19030,7 +19031,7 @@
         <v>393</v>
       </c>
       <c r="E799" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F799" t="s">
         <v>871</v>
@@ -19050,7 +19051,7 @@
         <v>393</v>
       </c>
       <c r="E800" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F800" t="s">
         <v>871</v>
@@ -19070,7 +19071,7 @@
         <v>393</v>
       </c>
       <c r="E801" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F801" t="s">
         <v>871</v>
@@ -19090,7 +19091,7 @@
         <v>393</v>
       </c>
       <c r="E802" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F802" t="s">
         <v>871</v>
@@ -19110,7 +19111,7 @@
         <v>393</v>
       </c>
       <c r="E803" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F803" t="s">
         <v>871</v>
@@ -19130,7 +19131,7 @@
         <v>393</v>
       </c>
       <c r="E804" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F804" t="s">
         <v>871</v>
@@ -19150,7 +19151,7 @@
         <v>393</v>
       </c>
       <c r="E805" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F805" t="s">
         <v>871</v>
@@ -19170,7 +19171,7 @@
         <v>393</v>
       </c>
       <c r="E806" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F806" t="s">
         <v>871</v>
@@ -19190,7 +19191,7 @@
         <v>393</v>
       </c>
       <c r="E807" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F807" t="s">
         <v>871</v>
@@ -19210,7 +19211,7 @@
         <v>393</v>
       </c>
       <c r="E808" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F808" t="s">
         <v>871</v>
@@ -19230,7 +19231,7 @@
         <v>393</v>
       </c>
       <c r="E809" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F809" t="s">
         <v>871</v>
@@ -19250,7 +19251,7 @@
         <v>393</v>
       </c>
       <c r="E810" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F810" t="s">
         <v>871</v>
@@ -19270,7 +19271,7 @@
         <v>393</v>
       </c>
       <c r="E811" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F811" t="s">
         <v>871</v>
@@ -19290,7 +19291,7 @@
         <v>393</v>
       </c>
       <c r="E812" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F812" t="s">
         <v>871</v>
@@ -19310,7 +19311,7 @@
         <v>393</v>
       </c>
       <c r="E813" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F813" t="s">
         <v>871</v>
@@ -19330,7 +19331,7 @@
         <v>393</v>
       </c>
       <c r="E814" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F814" t="s">
         <v>871</v>
@@ -19350,7 +19351,7 @@
         <v>393</v>
       </c>
       <c r="E815" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F815" t="s">
         <v>871</v>
@@ -19370,7 +19371,7 @@
         <v>393</v>
       </c>
       <c r="E816" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F816" t="s">
         <v>871</v>
@@ -19390,7 +19391,7 @@
         <v>393</v>
       </c>
       <c r="E817" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F817" t="s">
         <v>871</v>
@@ -19410,7 +19411,7 @@
         <v>393</v>
       </c>
       <c r="E818" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F818" t="s">
         <v>871</v>
@@ -19430,7 +19431,7 @@
         <v>393</v>
       </c>
       <c r="E819" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F819" t="s">
         <v>871</v>
@@ -19450,7 +19451,7 @@
         <v>393</v>
       </c>
       <c r="E820" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F820" t="s">
         <v>871</v>
@@ -19470,7 +19471,7 @@
         <v>393</v>
       </c>
       <c r="E821" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F821" t="s">
         <v>871</v>
@@ -19490,7 +19491,7 @@
         <v>393</v>
       </c>
       <c r="E822" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F822" t="s">
         <v>871</v>
@@ -19510,7 +19511,7 @@
         <v>393</v>
       </c>
       <c r="E823" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F823" t="s">
         <v>871</v>
@@ -19530,7 +19531,7 @@
         <v>393</v>
       </c>
       <c r="E824" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F824" t="s">
         <v>871</v>
@@ -19550,7 +19551,7 @@
         <v>393</v>
       </c>
       <c r="E825" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F825" t="s">
         <v>871</v>
@@ -19570,7 +19571,7 @@
         <v>393</v>
       </c>
       <c r="E826" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F826" t="s">
         <v>871</v>
@@ -19590,7 +19591,7 @@
         <v>393</v>
       </c>
       <c r="E827" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F827" t="s">
         <v>871</v>
@@ -19610,7 +19611,7 @@
         <v>393</v>
       </c>
       <c r="E828" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F828" t="s">
         <v>871</v>
@@ -19630,7 +19631,7 @@
         <v>393</v>
       </c>
       <c r="E829" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F829" t="s">
         <v>871</v>
@@ -19650,7 +19651,7 @@
         <v>393</v>
       </c>
       <c r="E830" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F830" t="s">
         <v>871</v>
@@ -19670,7 +19671,7 @@
         <v>393</v>
       </c>
       <c r="E831" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F831" t="s">
         <v>871</v>
@@ -19690,7 +19691,7 @@
         <v>393</v>
       </c>
       <c r="E832" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F832" t="s">
         <v>871</v>
@@ -19710,7 +19711,7 @@
         <v>393</v>
       </c>
       <c r="E833" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F833" t="s">
         <v>871</v>
@@ -19730,7 +19731,7 @@
         <v>393</v>
       </c>
       <c r="E834" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F834" t="s">
         <v>871</v>
@@ -19750,7 +19751,7 @@
         <v>393</v>
       </c>
       <c r="E835" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F835" t="s">
         <v>871</v>
@@ -19770,7 +19771,7 @@
         <v>393</v>
       </c>
       <c r="E836" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F836" t="s">
         <v>871</v>
@@ -19790,7 +19791,7 @@
         <v>393</v>
       </c>
       <c r="E837" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F837" t="s">
         <v>871</v>
@@ -19810,7 +19811,7 @@
         <v>393</v>
       </c>
       <c r="E838" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F838" t="s">
         <v>871</v>
@@ -19830,7 +19831,7 @@
         <v>393</v>
       </c>
       <c r="E839" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F839" t="s">
         <v>871</v>
@@ -19850,7 +19851,7 @@
         <v>393</v>
       </c>
       <c r="E840" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F840" t="s">
         <v>871</v>
@@ -19870,7 +19871,7 @@
         <v>393</v>
       </c>
       <c r="E841" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F841" t="s">
         <v>871</v>
@@ -19890,7 +19891,7 @@
         <v>393</v>
       </c>
       <c r="E842" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F842" t="s">
         <v>871</v>
@@ -19910,7 +19911,7 @@
         <v>393</v>
       </c>
       <c r="E843" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F843" t="s">
         <v>871</v>
@@ -19930,7 +19931,7 @@
         <v>393</v>
       </c>
       <c r="E844" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F844" t="s">
         <v>871</v>
@@ -19950,7 +19951,7 @@
         <v>393</v>
       </c>
       <c r="E845" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F845" t="s">
         <v>871</v>
@@ -19970,7 +19971,7 @@
         <v>393</v>
       </c>
       <c r="E846" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F846" t="s">
         <v>871</v>
@@ -19990,7 +19991,7 @@
         <v>393</v>
       </c>
       <c r="E847" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F847" t="s">
         <v>871</v>
@@ -20010,7 +20011,7 @@
         <v>393</v>
       </c>
       <c r="E848" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F848" t="s">
         <v>871</v>
@@ -20030,7 +20031,7 @@
         <v>393</v>
       </c>
       <c r="E849" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F849" t="s">
         <v>871</v>
@@ -20050,7 +20051,7 @@
         <v>393</v>
       </c>
       <c r="E850" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F850" t="s">
         <v>871</v>
@@ -20070,7 +20071,7 @@
         <v>393</v>
       </c>
       <c r="E851" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F851" t="s">
         <v>871</v>
@@ -20090,7 +20091,7 @@
         <v>393</v>
       </c>
       <c r="E852" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F852" t="s">
         <v>871</v>
@@ -20110,7 +20111,7 @@
         <v>393</v>
       </c>
       <c r="E853" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F853" t="s">
         <v>871</v>
@@ -20130,7 +20131,7 @@
         <v>393</v>
       </c>
       <c r="E854" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F854" t="s">
         <v>871</v>
@@ -20150,7 +20151,7 @@
         <v>393</v>
       </c>
       <c r="E855" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F855" t="s">
         <v>871</v>
@@ -20170,7 +20171,7 @@
         <v>393</v>
       </c>
       <c r="E856" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F856" t="s">
         <v>871</v>
@@ -20190,7 +20191,7 @@
         <v>393</v>
       </c>
       <c r="E857" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F857" t="s">
         <v>871</v>
